--- a/docs/exports/pathwave_dev_checklist.xlsx
+++ b/docs/exports/pathwave_dev_checklist.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="0.0%;-0.0%;-"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,36 +31,41 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <color rgb="000000FF"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <color rgb="00008000"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="맑은 고딕"/>
       <color rgb="00505050"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -122,9 +127,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -136,13 +142,13 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -151,10 +157,10 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -535,154 +541,181 @@
           <t>PathWave 개발 체크리스트 요약</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>지표</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
+      <c r="C3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>총 PR 수</t>
         </is>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <f>COUNTA('PR 체크리스트'!A2:A30)</f>
         <v/>
       </c>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>완료 (✅)</t>
         </is>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <f>COUNTIF('PR 체크리스트'!F2:F30,"✅")</f>
         <v/>
       </c>
+      <c r="C5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>검토중 (🔎)</t>
         </is>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="5">
         <f>COUNTIF('PR 체크리스트'!F2:F30,"🔎")</f>
         <v/>
       </c>
+      <c r="C6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>부분 완료 (◑)</t>
         </is>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <f>COUNTIF('PR 체크리스트'!F2:F30,"◑")</f>
         <v/>
       </c>
+      <c r="C7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>진행중 (🔄)</t>
         </is>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <f>COUNTIF('PR 체크리스트'!F2:F30,"🔄")</f>
         <v/>
       </c>
+      <c r="C8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>대기 (⬜)</t>
         </is>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <f>COUNTIF('PR 체크리스트'!F2:F30,"⬜")</f>
         <v/>
       </c>
+      <c r="C9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>가중 평균 진척율</t>
         </is>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="6">
         <f>AVERAGE('PR 체크리스트'!G2:G30)</f>
         <v/>
       </c>
+      <c r="C10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>업데이트 일자</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
+      <c r="C11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>목표 출시일</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>2026-07-하순~8월 초</t>
         </is>
       </c>
+      <c r="C12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>사용 방법</t>
         </is>
       </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>① "PR 체크리스트" 시트에서 F열(상태) 드롭다운으로 ⬜ → 🔄 → 🔎 → ✅ 갱신</t>
         </is>
       </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>② I/J/K열(시작일·목표일·완료일)을 yyyy-mm-dd 로 입력하면 일정 추적 가능</t>
         </is>
       </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>③ 진척율은 상태에 따라 자동 계산 (⬜=0%, 🔄=50%, ◑=70%, 🔎=90%, ✅=100%)</t>
         </is>
       </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>④ 요약 시트는 PR 체크리스트의 상태를 실시간 집계</t>
         </is>
       </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -716,1237 +749,1237 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>분류</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>도메인</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>콘솔/영역</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>내용 요약</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>진척율</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>담당</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>시작일</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>목표일</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>완료일</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>검증 시나리오 / 메모</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>mobile 디자인 기반</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>mobile</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>테마 단일화 + 시스템 폰트 + neu/ 위젯 통합 + Pw* 4종 추가</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="12">
         <f>IF(F2="✅",1,IF(F2="🔄",0.5,IF(F2="◑",0.7,IF(F2="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
+      <c r="I2" s="14" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J2" s="13" t="inlineStr">
+      <c r="J2" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K2" s="13" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>시뮬레이터 렌더 확인, 위젯 일관성</t>
         </is>
       </c>
-      <c r="L2" s="9" t="n"/>
+      <c r="L2" s="10" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>mobile i18n</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>mobile·BE</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>I18nService DB 통일 + 12언어 + 전 화면 t() 전환 + ko 시드 550 + DeepL 스크립트</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="12">
         <f>IF(F3="✅",1,IF(F3="🔄",0.5,IF(F3="◑",0.7,IF(F3="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J3" s="13" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>전 화면 grep clean, flutter analyze pass</t>
         </is>
       </c>
-      <c r="L3" s="9" t="n"/>
+      <c r="L3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>웹 디자인 시스템</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>provider·admin</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>alert/confirm 33곳→useDialog 공용 모달 + 색 토큰 정합</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="12">
         <f>IF(F4="✅",1,IF(F4="🔄",0.5,IF(F4="◑",0.7,IF(F4="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K4" s="13" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>두 콘솔 build + grep clean</t>
         </is>
       </c>
-      <c r="L4" s="9" t="n"/>
+      <c r="L4" s="10" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>인증 우회 제거</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>provider·admin·BE</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>DEV_AUTO_LOGIN env 게이트 + 실 로그인폼 복구 + /forgot-password 정식 구현(BE 2 API + 페이지)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="12">
         <f>IF(F5="✅",1,IF(F5="🔄",0.5,IF(F5="◑",0.7,IF(F5="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J5" s="13" t="inlineStr">
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>BE 2 API test client 통과(미존재 이메일 200/잘못된 코드 400). ⚠ app.py 재시작 필요</t>
         </is>
       </c>
-      <c r="L5" s="9" t="n"/>
+      <c r="L5" s="10" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>매장·회사정보 실연동</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>provider</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>StoreInfo 하드코딩 제거 + StoreService 실연동 + PwFooter + dead code Facilities 삭제</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="12">
         <f>IF(F6="✅",1,IF(F6="🔄",0.5,IF(F6="◑",0.7,IF(F6="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J6" s="13" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K6" s="13" t="inlineStr">
+      <c r="K6" s="14" t="inlineStr">
         <is>
           <t>res.facilities 데이터 접근 검증, build 통과</t>
         </is>
       </c>
-      <c r="L6" s="9" t="n"/>
+      <c r="L6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>OCR 허위 제거</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>provider</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>WifiSettings·ServiceRequest runOcrMock 제거 → 정직한 수동입력 UI</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="12">
         <f>IF(F7="✅",1,IF(F7="🔄",0.5,IF(F7="◑",0.7,IF(F7="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J7" s="13" t="inlineStr">
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t>OCR 잔여 참조 0건 grep, build 통과</t>
         </is>
       </c>
-      <c r="L7" s="9" t="n"/>
+      <c r="L7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>결제·구독 실연동</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>provider·admin</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>카드 localStorage 평문저장 제거(PCI) + BillingService + Payment/Subscription/ServiceRequest 실연동</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="12">
         <f>IF(F8="✅",1,IF(F8="🔄",0.5,IF(F8="◑",0.7,IF(F8="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K8" s="13" t="inlineStr">
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t>localStorage 카드저장 0건 + PAN/CVC 전송 0건 grep, build 통과</t>
         </is>
       </c>
-      <c r="L8" s="9" t="n"/>
+      <c r="L8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>채팅 도메인</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>mobile·provider·admin·BE</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>provider CustomerChat 실연동 + admin ChatMonitor + BE /api/chat/reports + mobile SSE 재연결</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>◑</t>
         </is>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="12">
         <f>IF(F9="✅",1,IF(F9="🔄",0.5,IF(F9="◑",0.7,IF(F9="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="K9" s="14" t="inlineStr">
         <is>
           <t>번역=P8b 분리. BE 라우트 등록/401 가드 검증. ⚠ app.py 재시작 필요</t>
         </is>
       </c>
-      <c r="L9" s="9" t="n"/>
+      <c r="L9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>P8b</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>채팅 자동 번역</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>mobile·provider·BE</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>chat_messages 번역 캐시 스키마 + 뷰어별 언어 + translator↔chat 연결</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="12">
         <f>IF(F10="✅",1,IF(F10="🔄",0.5,IF(F10="◑",0.7,IF(F10="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>키 확보 후</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr"/>
-      <c r="K10" s="13" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr"/>
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t>Google/DeepL 키 확보(출시 2단계) 후 진행 — USP 기능</t>
         </is>
       </c>
-      <c r="L10" s="9" t="n"/>
+      <c r="L10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>쿠폰·스탬프 실연동</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>mobile·provider</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Coupons·Stamps mock→실연동 + 쿠폰 사용 silent error 수정</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="12">
         <f>IF(F11="✅",1,IF(F11="🔄",0.5,IF(F11="◑",0.7,IF(F11="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="13" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr"/>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="J11" s="14" t="inlineStr"/>
+      <c r="K11" s="14" t="inlineStr">
         <is>
           <t>캐셔 게이트는 P22</t>
         </is>
       </c>
-      <c r="L11" s="9" t="n"/>
+      <c r="L11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>알림 도메인</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>mobile·provider·admin</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>provider Notifications 실연동 + mobile 알림 라우팅 + 알림 탭 보강</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="12">
         <f>IF(F12="✅",1,IF(F12="🔄",0.5,IF(F12="◑",0.7,IF(F12="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr"/>
-      <c r="K12" s="13" t="inlineStr"/>
-      <c r="L12" s="9" t="n"/>
+      <c r="J12" s="14" t="inlineStr"/>
+      <c r="K12" s="14" t="inlineStr"/>
+      <c r="L12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>대시보드·직원</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>provider·admin·BE</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Dashboard·StaffManagement 실연동 + admin 가짜데이터 제거 + StaffMonitor·CouponStats placeholder 해소</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="12">
         <f>IF(F13="✅",1,IF(F13="🔄",0.5,IF(F13="◑",0.7,IF(F13="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr"/>
-      <c r="K13" s="13" t="inlineStr"/>
-      <c r="L13" s="9" t="n"/>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14" t="inlineStr"/>
+      <c r="L13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>mobile 심의 직격 화면</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>mobile·BE</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>consent placeholder 제거 + 동의 로드 실패 복구 + settings dev 정보 제거 + 앱 버전 동적화</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="12">
         <f>IF(F14="✅",1,IF(F14="🔄",0.5,IF(F14="◑",0.7,IF(F14="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="13" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr"/>
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr"/>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="J14" s="14" t="inlineStr"/>
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>심의 직격 — 출시 전 필수</t>
         </is>
       </c>
-      <c r="L14" s="9" t="n"/>
+      <c r="L14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>약관 3종</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>mobile·provider·admin·BE</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>환불·청소년·쿠키 정책 BE/admin/노출 + policy_view 언어 정합</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="12">
         <f>IF(F15="✅",1,IF(F15="🔄",0.5,IF(F15="◑",0.7,IF(F15="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J15" s="13" t="inlineStr"/>
-      <c r="K15" s="13" t="inlineStr"/>
-      <c r="L15" s="9" t="n"/>
+      <c r="J15" s="14" t="inlineStr"/>
+      <c r="K15" s="14" t="inlineStr"/>
+      <c r="L15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>WiFi 데이터 모델 재설계</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>wifi_profiles 확장 + beacon_wifi·units·grant·devices 신규 + beacons.role</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="12">
         <f>IF(F16="✅",1,IF(F16="🔄",0.5,IF(F16="◑",0.7,IF(F16="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>2026-06-말~7월초</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr"/>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr"/>
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>P15~P19 기반</t>
         </is>
       </c>
-      <c r="L16" s="9" t="n"/>
+      <c r="L16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>WiFi 등록·연동</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>provider·admin·BE</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>handshake 묶음 반환 + admin WiFi 등록화면 + provider WifiSettings 실연동 + 비콘 role UI</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="12">
         <f>IF(F17="✅",1,IF(F17="🔄",0.5,IF(F17="◑",0.7,IF(F17="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H17" s="12" t="inlineStr"/>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>2026-07-초</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr"/>
-      <c r="K17" s="13" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>C10·C13 해소</t>
         </is>
       </c>
-      <c r="L17" s="9" t="n"/>
+      <c r="L17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>mobile WiFi 클라이언트</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>mobile</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>비콘→WiFi 묶음 fetch·캐시 + BSSID 검증 + 손님 자동/승인 + home 보강</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="12">
         <f>IF(F18="✅",1,IF(F18="🔄",0.5,IF(F18="◑",0.7,IF(F18="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H18" s="12" t="inlineStr"/>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr"/>
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>2026-07-초</t>
         </is>
       </c>
-      <c r="J18" s="13" t="inlineStr"/>
-      <c r="K18" s="13" t="inlineStr"/>
-      <c r="L18" s="9" t="n"/>
+      <c r="J18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="inlineStr"/>
+      <c r="L18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>P17</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>.mobileconfig 다건 설치</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>BE·mobile·iOS</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>.mobileconfig 생성·다건 설치 (서명은 인증서 도착 후)</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="12">
         <f>IF(F19="✅",1,IF(F19="🔄",0.5,IF(F19="◑",0.7,IF(F19="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H19" s="12" t="inlineStr"/>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J19" s="13" t="inlineStr"/>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr"/>
+      <c r="K19" s="14" t="inlineStr">
         <is>
           <t>서명은 Apple 인증서 확보 후 적용</t>
         </is>
       </c>
-      <c r="L19" s="9" t="n"/>
+      <c r="L19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>P18</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>credential_mode managed</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>BE·provider·mobile</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>비번 교체 리마인드 + 인가 손님 자동 전파</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="12">
         <f>IF(F20="✅",1,IF(F20="🔄",0.5,IF(F20="◑",0.7,IF(F20="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H20" s="12" t="inlineStr"/>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr"/>
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr"/>
-      <c r="K20" s="13" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr"/>
+      <c r="K20" s="14" t="inlineStr">
         <is>
           <t>v1 flag — 코드만 완성, UI 비공개</t>
         </is>
       </c>
-      <c r="L20" s="9" t="n"/>
+      <c r="L20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>P19</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>units/grant 관리 화면</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>admin·provider·BE</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>호실·자리 시간제 권한 관리 UI</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="12">
         <f>IF(F21="✅",1,IF(F21="🔄",0.5,IF(F21="◑",0.7,IF(F21="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H21" s="12" t="inlineStr"/>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J21" s="13" t="inlineStr"/>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr"/>
+      <c r="K21" s="14" t="inlineStr">
         <is>
           <t>v1 flag — 코드만 완성, UI 비공개</t>
         </is>
       </c>
-      <c r="L21" s="9" t="n"/>
+      <c r="L21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>P20</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>심의 마무리</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>앱 버전관리</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>admin·mobile</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>admin app-versions UI(BE 완성) + mobile OS 최소버전 게이트</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="12">
         <f>IF(F22="✅",1,IF(F22="🔄",0.5,IF(F22="◑",0.7,IF(F22="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr"/>
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr"/>
-      <c r="K22" s="13" t="inlineStr"/>
-      <c r="L22" s="9" t="n"/>
+      <c r="J22" s="14" t="inlineStr"/>
+      <c r="K22" s="14" t="inlineStr"/>
+      <c r="L22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>P21</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>심의 마무리</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>심의 메타 자산</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>mobile·iOS</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>PrivacyInfo.xcprivacy + Bundle ID 확정 + Android Photo Picker + 계정삭제 웹 URL</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="12">
         <f>IF(F23="✅",1,IF(F23="🔄",0.5,IF(F23="◑",0.7,IF(F23="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="13" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J23" s="13" t="inlineStr"/>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr"/>
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>심의 reject 방지 필수</t>
         </is>
       </c>
-      <c r="L23" s="9" t="n"/>
+      <c r="L23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>P22</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>회원 QR 운영</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>쿠폰·스탬프 회원 QR</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>mobile·provider·BE</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>회원 QR(URL 토큰) + provider 스캔/코드입력 → 적립·사용 + 친구초대 QR/링크</t>
         </is>
       </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="12">
         <f>IF(F24="✅",1,IF(F24="🔄",0.5,IF(F24="◑",0.7,IF(F24="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H24" s="12" t="inlineStr"/>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr"/>
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>2026-07-초~중</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr"/>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr"/>
+      <c r="K24" s="14" t="inlineStr">
         <is>
           <t>P9 이후 병행</t>
         </is>
       </c>
-      <c r="L24" s="9" t="n"/>
+      <c r="L24" s="10" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1975,227 +2008,227 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>단계</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>예상 기간</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>누적</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>P1~P3</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>~4일</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>5월 말</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Critical 도메인</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>P4~P13 (10 PR)</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>~2주</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>6월 중순</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>P4~P8 완료, 나머지 진행 예정</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>WiFi 로밍 (B 풀스코프)</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>P14~P19 (6 PR)</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>~2.5~3주</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>7월 초~중순</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>feature flag로 P18·P19 v1 비공개</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>쿠폰·스탬프 회원 QR</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>P22 (P9 이후 병행)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>~1주</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>7월 초~중순</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
+      <c r="E5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>심의 마무리</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>P20~P21</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>~3일</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>7월 중순</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Phase 2~4 테스트·시드</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>테스트데이터 시드 + 페르소나 검증</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>~1.5주</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>7월 중순~하순</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Phase 5 제출 준비</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>빌드 + 스토어 메타데이터</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>며칠</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>7월 하순</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>출시</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>앱스토어/플레이 공개</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>7월 하순~8월 초</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/exports/pathwave_dev_checklist.xlsx
+++ b/docs/exports/pathwave_dev_checklist.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PR 체크리스트" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단계별 일정" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기능별 전체 현황" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1 PR 체크리스트" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="단계별 일정" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,13 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="000000FF"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -42,12 +49,7 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
+      <color rgb="000000FF"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
@@ -68,7 +70,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -77,17 +79,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,40 +139,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -528,11 +546,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,11 +583,11 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>총 PR 수</t>
+          <t>총 PR 수 (Phase 1)</t>
         </is>
       </c>
       <c r="B4" s="5">
-        <f>COUNTA('PR 체크리스트'!A2:A30)</f>
+        <f>COUNTA('Phase 1 PR 체크리스트'!A2:A30)</f>
         <v/>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -581,7 +599,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('PR 체크리스트'!F2:F30,"✅")</f>
+        <f>COUNTIF('Phase 1 PR 체크리스트'!F2:F30,"✅")</f>
         <v/>
       </c>
       <c r="C5" s="2" t="n"/>
@@ -589,11 +607,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>검토중 (🔎)</t>
+          <t>부분 완료 (◑)</t>
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('PR 체크리스트'!F2:F30,"🔎")</f>
+        <f>COUNTIF('Phase 1 PR 체크리스트'!F2:F30,"◑")</f>
         <v/>
       </c>
       <c r="C6" s="2" t="n"/>
@@ -601,11 +619,11 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>부분 완료 (◑)</t>
+          <t>진행중 (🔄)</t>
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('PR 체크리스트'!F2:F30,"◑")</f>
+        <f>COUNTIF('Phase 1 PR 체크리스트'!F2:F30,"🔄")</f>
         <v/>
       </c>
       <c r="C7" s="2" t="n"/>
@@ -613,11 +631,11 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>진행중 (🔄)</t>
+          <t>검토중 (🔎)</t>
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF('PR 체크리스트'!F2:F30,"🔄")</f>
+        <f>COUNTIF('Phase 1 PR 체크리스트'!F2:F30,"🔎")</f>
         <v/>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -629,7 +647,7 @@
         </is>
       </c>
       <c r="B9" s="5">
-        <f>COUNTIF('PR 체크리스트'!F2:F30,"⬜")</f>
+        <f>COUNTIF('Phase 1 PR 체크리스트'!F2:F30,"⬜")</f>
         <v/>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -641,7 +659,7 @@
         </is>
       </c>
       <c r="B10" s="6">
-        <f>AVERAGE('PR 체크리스트'!G2:G30)</f>
+        <f>AVERAGE('Phase 1 PR 체크리스트'!G2:G30)</f>
         <v/>
       </c>
       <c r="C10" s="2" t="n"/>
@@ -662,29 +680,33 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>외부 서비스 신청 시작</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-02 주 (법인카드 수취 후)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>목표 출시일</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>2026-07-하순~8월 초</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="C13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>사용 방법</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>① "PR 체크리스트" 시트에서 F열(상태) 드롭다운으로 ⬜ → 🔄 → 🔎 → ✅ 갱신</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -693,7 +715,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>② I/J/K열(시작일·목표일·완료일)을 yyyy-mm-dd 로 입력하면 일정 추적 가능</t>
+          <t>① "기능별 전체 현황": 도메인별 이전 완료/Phase 1/남은 작업을 한눈에</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -702,7 +724,7 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>③ 진척율은 상태에 따라 자동 계산 (⬜=0%, 🔄=50%, ◑=70%, 🔎=90%, ✅=100%)</t>
+          <t>② "Phase 1 PR 체크리스트": F열 상태 드롭다운(⬜→🔄→🔎→◑→✅) 갱신</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -711,11 +733,29 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>④ 요약 시트는 PR 체크리스트의 상태를 실시간 집계</t>
+          <t>③ 진척율 자동 계산: ⬜=0% · 🔄=50% · ◑=70% · 🔎=90% · ✅=100%</t>
         </is>
       </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>④ "단계별 일정": 출시까지의 큰 그림 일정</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>⑤ 요약은 PR 체크리스트 상태를 실시간 집계</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -726,6 +766,1263 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PathWave 기능별 전체 작업 현황 — 이전 완료 + Phase 1 진행 + 남은 작업</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>도메인/기능</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>PR #1~#5, #28, #45, #55</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>이메일 가입·로그인, 5종 소셜 로그인(Google/Apple/Facebook/Kakao/Naver), 동의 단계, 미성년자 보호, 회원 탈퇴 흐름</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>코드 완료, 실 키는 서비스 가입 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>dev 인증 우회 제거 + 실 로그인폼 복구 + /forgot-password 정식 구현</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>BE 2 API + provider 페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>실 키 검증</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Firebase·카카오·네이버 실 키로 통합 테스트 (서비스 가입 후)</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>외부 서비스 활성화 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>PR #2, #14, #16</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>매장 CRUD, 이미지 갤러리, 다국어 번역 캐시</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>StoreInfo 하드코딩 제거 + StoreService 실연동 + PwFooter + dead code 정리</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>백엔드 schema 부재(category/holidays) → P8c 별도 작업</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>P8c (별도 작업 칩)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>facilities 스키마 category/holidays/detailAddress 컬럼 추가 또는 UI 정리</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>결정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>PR #39, #41, #43~46, #56</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>billing API 전체(cards/subscriptions/payments/refund/extend), PG provider 추상화</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>백엔드 sim 모드 — 토스 키 활성화 시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>P7</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>provider 카드 평문저장 제거(PCI) + BillingService + Payment/Subscription/ServiceRequest 실연동</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>admin Payments는 이미 정합</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>토스 키 활성화</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>토스페이먼츠 가맹점 심사 통과 후 PG_PROVIDER=toss + 실 결제 검증</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>외부(심사 1~2주)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>쿠폰·스탬프</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>PR #6, #18, #22, #29</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>쿠폰 발행/사용/만료, 스탬프 적립/리워드, 정책 설정</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>쿠폰·스탬프</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>P9</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>provider Coupons·Stamps mock→실연동 + mobile 쿠폰 사용 silent error 수정</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>쿠폰·스탬프</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>회원 QR (URL 토큰 인코딩) + provider 스캔/코드입력 → 적립/사용 + 친구초대 QR/링크</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>P9 이후 병행</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>PR #16, #21, #142</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>1:1 채팅 rooms/messages, SSE 스트림, 신고/차단</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>P8 (◑)</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>provider CustomerChat 실연동 + admin ChatMonitor + BE /api/chat/reports + mobile SSE 재연결</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>◑</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>⚠ app.py 재시작 후 활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>P8b</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>채팅 자동 번역(번역 캐시 스키마 + 뷰어별 언어 + translator 연결)</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>DeepL/Google Translate 키 확보 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>알림 (Inbox + Push)</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>PR #38, #44, #50</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Inbox·Announcements, FCM 푸시, APNs(HTTP/2 JWT), 알림 선호 카테고리</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>알림 (Inbox + Push)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>provider Notifications 실연동 + mobile 알림 라우팅 + 알림 탭 보강</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>WiFi (1회 연결)</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>PR #11, #49</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>wifi_profiles 기본, native plugin(iOS/Android) 자동 가입 요청, BLE 핸드셰이크</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>1회 연결만, 로밍 미지원</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>WiFi 로밍 (B 풀스코프)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>P14~P19</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>wifi_profiles 확장 + beacon_wifi·units·grant·devices + admin/provider 등록 + mobile 클라이언트 + .mobileconfig 다건 + managed/units (flag)</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>6월 말~7월 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>비콘 (인벤토리/claim/모니터)</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>PR #37, #38</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>admin 인벤토리 CSV 입고, provider claim, 배터리 모니터링, 펌웨어 표시</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>비콘</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>P15 (병합)</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>beacons.role(wifi/cashier) 추가 + admin·provider UI</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>i18n (12언어)</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>BE translations API + admin CRUD</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>백엔드 translations 테이블, DeepL 통합, 12개 supportedLocales, admin CRUD</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>mobile I18nService DB 통일 + 전 화면 t() 전환 + ko 시드 550 + DeepL 일괄번역 스크립트</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>11개 언어 번역 = DeepL 키 확보 후 batch 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>DeepL 번역 batch</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>translations DB의 ko 키 → 11개 언어 자동 번역(약 22 × 549건)</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>DeepL API 키 활성화 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>8종 KIND 등록</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>terms, privacy, location, marketing, push, camera, storage, third_party, age14 DB 등록</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>환불·청소년·쿠키 정책 3종 BE/admin/노출 추가 + policy_view 언어 정합</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>3콘솔 디자인 정합</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>mobile dark + 보라, provider-web dark + 녹색, admin-web dark + 블루 — 3콘솔 디자인 토큰 통일</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>P1·P3</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>mobile 테마 단일화 + 시스템 폰트 + Pw* 위젯 / 웹 alert·confirm 33곳 → 공용 모달</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>슈퍼어드민 (admin-web)</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>PR #36~#39, #142</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Login + Dashboard + Beacons + Approvals + Battery + Announcements + Payments + Subscriptions + Policies + Reports + Translations + Audit</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>P11·P20</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard 가짜데이터 제거 + StaffMonitor·CouponStats placeholder 해소 + app-versions UI(BE 완성)</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>백엔드 staff API</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>직원 초대/권한/관리 백엔드</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>provider StaffManagement 실연동 + admin StaffMonitor 실연동</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>심의 직격 (mobile)</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>consent placeholder 제거 + 동의 로드 실패 복구 + settings dev 정보 제거 + 앱 버전 동적화</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>심의 reject 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>심의 메타 자산</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>PrivacyInfo.xcprivacy + Bundle ID 확정 + Android Photo Picker + 계정삭제 웹 URL</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>iOS/Android 심사 필수</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>OCR 허위 제거</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>WifiSettings·ServiceRequest runOcrMock 제거 → 정직한 수동입력 UI</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>심의 reject 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>회사 정보 (footer)</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>P5 (포함)</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>Settings 푸터 → PwFooter (CompanyInfoService → 트리거소프트 실 법인정보)</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>법인 등기 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>PR #35, #41, #51</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>SECRET_KEY/AES_KEY ENV + CORS 화이트리스트 + rate-limit + gunicorn/wsgi + Sentry + PostgreSQL 어댑터</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>실 호스팅은 외부 서비스 활성화 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Phase 2~4 테스트</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>W7 테스트 시드</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>6 페르소나(외국인/한국인/소규모/중대형/직원/슈퍼어드민) 테스트 데이터 시드 + 시나리오 검증</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>7월 중순~하순</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Phase 5 제출</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>스토어 제출</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>iOS/Android 빌드 + 스토어 메타데이터 + 스크린샷 + 심의 제출</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>7월 하순~8월 초</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -745,10 +2042,10 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
           <t>PR</t>
@@ -811,29 +2108,29 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="12" t="inlineStr">
         <is>
           <t>mobile 디자인 기반</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>mobile</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>테마 단일화 + 시스템 폰트 + neu/ 위젯 통합 + Pw* 4종 추가</t>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>테마 단일화 + 시스템 폰트 + Pw* 위젯 4종</t>
         </is>
       </c>
       <c r="F2" s="11" t="inlineStr">
@@ -841,56 +2138,52 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="16">
         <f>IF(F2="✅",1,IF(F2="🔄",0.5,IF(F2="◑",0.7,IF(F2="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H2" s="13" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="I2" s="18" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J2" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K2" s="14" t="inlineStr">
-        <is>
-          <t>시뮬레이터 렌더 확인, 위젯 일관성</t>
-        </is>
-      </c>
-      <c r="L2" s="10" t="n"/>
+      <c r="K2" s="18" t="inlineStr"/>
+      <c r="L2" s="12" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>mobile i18n</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>mobile·BE</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>I18nService DB 통일 + 12언어 + 전 화면 t() 전환 + ko 시드 550 + DeepL 스크립트</t>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>12언어 단일화 + 전 화면 t() + ko 시드 550 + DeepL 스크립트</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
@@ -898,56 +2191,52 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="16">
         <f>IF(F3="✅",1,IF(F3="🔄",0.5,IF(F3="◑",0.7,IF(F3="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H3" s="13" t="inlineStr">
+      <c r="H3" s="17" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K3" s="14" t="inlineStr">
-        <is>
-          <t>전 화면 grep clean, flutter analyze pass</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="n"/>
+      <c r="K3" s="18" t="inlineStr"/>
+      <c r="L3" s="12" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>웹 디자인 시스템</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>provider·admin</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>alert/confirm 33곳→useDialog 공용 모달 + 색 토큰 정합</t>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>alert/confirm 33곳 → useDialog 공용 모달 + 색 토큰</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -955,56 +2244,52 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="16">
         <f>IF(F4="✅",1,IF(F4="🔄",0.5,IF(F4="◑",0.7,IF(F4="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="17" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
-        <is>
-          <t>두 콘솔 build + grep clean</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="n"/>
+      <c r="K4" s="18" t="inlineStr"/>
+      <c r="L4" s="12" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>인증 우회 제거</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>provider·admin·BE</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>DEV_AUTO_LOGIN env 게이트 + 실 로그인폼 복구 + /forgot-password 정식 구현(BE 2 API + 페이지)</t>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>DEV_AUTO_LOGIN env 게이트 + 실 로그인폼 + /forgot-password 정식</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -1012,56 +2297,56 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="16">
         <f>IF(F5="✅",1,IF(F5="🔄",0.5,IF(F5="◑",0.7,IF(F5="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="17" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>BE 2 API test client 통과(미존재 이메일 200/잘못된 코드 400). ⚠ app.py 재시작 필요</t>
-        </is>
-      </c>
-      <c r="L5" s="10" t="n"/>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t>⚠ app.py 재시작 필요</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>P5</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>매장·회사정보 실연동</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>provider</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>StoreInfo 하드코딩 제거 + StoreService 실연동 + PwFooter + dead code Facilities 삭제</t>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>StoreInfo 실연동 + PwFooter + dead code 정리</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -1069,56 +2354,52 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="16">
         <f>IF(F6="✅",1,IF(F6="🔄",0.5,IF(F6="◑",0.7,IF(F6="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
-        <is>
-          <t>res.facilities 데이터 접근 검증, build 통과</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="n"/>
+      <c r="K6" s="18" t="inlineStr"/>
+      <c r="L6" s="12" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>P6</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>OCR 허위 제거</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>provider</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>WifiSettings·ServiceRequest runOcrMock 제거 → 정직한 수동입력 UI</t>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>가짜 OCR 자동입력 제거 → 정직한 수동입력 UI</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1126,56 +2407,52 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="16">
         <f>IF(F7="✅",1,IF(F7="🔄",0.5,IF(F7="◑",0.7,IF(F7="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H7" s="13" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
-        <is>
-          <t>OCR 잔여 참조 0건 grep, build 통과</t>
-        </is>
-      </c>
-      <c r="L7" s="10" t="n"/>
+      <c r="K7" s="18" t="inlineStr"/>
+      <c r="L7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>P7</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>결제·구독 실연동</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>provider·admin</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>카드 localStorage 평문저장 제거(PCI) + BillingService + Payment/Subscription/ServiceRequest 실연동</t>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>카드 localStorage 제거(PCI) + BillingService + 실연동</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -1183,56 +2460,52 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="16">
         <f>IF(F8="✅",1,IF(F8="🔄",0.5,IF(F8="◑",0.7,IF(F8="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H8" s="13" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K8" s="14" t="inlineStr">
-        <is>
-          <t>localStorage 카드저장 0건 + PAN/CVC 전송 0건 grep, build 통과</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="n"/>
+      <c r="K8" s="18" t="inlineStr"/>
+      <c r="L8" s="12" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>P8</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>채팅 도메인</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>mobile·provider·admin·BE</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>provider CustomerChat 실연동 + admin ChatMonitor + BE /api/chat/reports + mobile SSE 재연결</t>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>provider CustomerChat + admin ChatMonitor + BE 신고 API + mobile SSE 재연결</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -1240,746 +2513,726 @@
           <t>◑</t>
         </is>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="16">
         <f>IF(F9="✅",1,IF(F9="🔄",0.5,IF(F9="◑",0.7,IF(F9="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K9" s="14" t="inlineStr">
-        <is>
-          <t>번역=P8b 분리. BE 라우트 등록/401 가드 검증. ⚠ app.py 재시작 필요</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="n"/>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>번역=P8b 분리, ⚠ app.py 재시작</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>P8b</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>채팅 자동 번역</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>mobile·provider·BE</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>chat_messages 번역 캐시 스키마 + 뷰어별 언어 + translator↔chat 연결</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>번역 캐시 스키마 + 뷰어별 언어 + translator↔chat 연결</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="16">
         <f>IF(F10="✅",1,IF(F10="🔄",0.5,IF(F10="◑",0.7,IF(F10="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H10" s="13" t="inlineStr"/>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr"/>
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>키 확보 후</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr"/>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>Google/DeepL 키 확보(출시 2단계) 후 진행 — USP 기능</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="n"/>
+      <c r="J10" s="18" t="inlineStr"/>
+      <c r="K10" s="18" t="inlineStr">
+        <is>
+          <t>Google/DeepL 키 확보 후</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>P9</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>쿠폰·스탬프 실연동</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>mobile·provider</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>Coupons·Stamps mock→실연동 + 쿠폰 사용 silent error 수정</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Coupons·Stamps mock→실연동</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="16">
         <f>IF(F11="✅",1,IF(F11="🔄",0.5,IF(F11="◑",0.7,IF(F11="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H11" s="13" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr"/>
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J11" s="14" t="inlineStr"/>
-      <c r="K11" s="14" t="inlineStr">
-        <is>
-          <t>캐셔 게이트는 P22</t>
-        </is>
-      </c>
-      <c r="L11" s="10" t="n"/>
+      <c r="J11" s="18" t="inlineStr"/>
+      <c r="K11" s="18" t="inlineStr"/>
+      <c r="L11" s="12" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>P10</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>알림 도메인</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>mobile·provider·admin</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>provider Notifications 실연동 + mobile 알림 라우팅 + 알림 탭 보강</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Notifications 실연동 + mobile 라우팅</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="16">
         <f>IF(F12="✅",1,IF(F12="🔄",0.5,IF(F12="◑",0.7,IF(F12="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H12" s="13" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr"/>
-      <c r="K12" s="14" t="inlineStr"/>
-      <c r="L12" s="10" t="n"/>
+      <c r="J12" s="18" t="inlineStr"/>
+      <c r="K12" s="18" t="inlineStr"/>
+      <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>P11</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>대시보드·직원</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>provider·admin·BE</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Dashboard·StaffManagement 실연동 + admin 가짜데이터 제거 + StaffMonitor·CouponStats placeholder 해소</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard·StaffManagement 실연동</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="16">
         <f>IF(F13="✅",1,IF(F13="🔄",0.5,IF(F13="◑",0.7,IF(F13="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H13" s="13" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr"/>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J13" s="14" t="inlineStr"/>
-      <c r="K13" s="14" t="inlineStr"/>
-      <c r="L13" s="10" t="n"/>
+      <c r="J13" s="18" t="inlineStr"/>
+      <c r="K13" s="18" t="inlineStr"/>
+      <c r="L13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>P12</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>mobile 심의 직격 화면</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>mobile 심의 직격</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>mobile·BE</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>consent placeholder 제거 + 동의 로드 실패 복구 + settings dev 정보 제거 + 앱 버전 동적화</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>consent placeholder + dev 정보 제거 + 앱 버전 동적화</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="16">
         <f>IF(F14="✅",1,IF(F14="🔄",0.5,IF(F14="◑",0.7,IF(F14="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr"/>
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr"/>
-      <c r="K14" s="14" t="inlineStr">
-        <is>
-          <t>심의 직격 — 출시 전 필수</t>
-        </is>
-      </c>
-      <c r="L14" s="10" t="n"/>
+      <c r="J14" s="18" t="inlineStr"/>
+      <c r="K14" s="18" t="inlineStr"/>
+      <c r="L14" s="12" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>P13</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>약관 3종</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>mobile·provider·admin·BE</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>환불·청소년·쿠키 정책 BE/admin/노출 + policy_view 언어 정합</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>환불·청소년·쿠키 정책</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="16">
         <f>IF(F15="✅",1,IF(F15="🔄",0.5,IF(F15="◑",0.7,IF(F15="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H15" s="13" t="inlineStr"/>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="H15" s="17" t="inlineStr"/>
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J15" s="14" t="inlineStr"/>
-      <c r="K15" s="14" t="inlineStr"/>
-      <c r="L15" s="10" t="n"/>
+      <c r="J15" s="18" t="inlineStr"/>
+      <c r="K15" s="18" t="inlineStr"/>
+      <c r="L15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>P14</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>WiFi 데이터 모델 재설계</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>WiFi 데이터 모델</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>wifi_profiles 확장 + beacon_wifi·units·grant·devices 신규 + beacons.role</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>wifi_profiles 확장 + beacon_wifi·units·grant·devices</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="16">
         <f>IF(F16="✅",1,IF(F16="🔄",0.5,IF(F16="◑",0.7,IF(F16="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="H16" s="17" t="inlineStr"/>
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>2026-06-말~7월초</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr"/>
-      <c r="K16" s="14" t="inlineStr">
-        <is>
-          <t>P15~P19 기반</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="n"/>
+      <c r="J16" s="18" t="inlineStr"/>
+      <c r="K16" s="18" t="inlineStr"/>
+      <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>P15</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>WiFi 등록·연동</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>provider·admin·BE</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>handshake 묶음 반환 + admin WiFi 등록화면 + provider WifiSettings 실연동 + 비콘 role UI</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>handshake 묶음 + admin WiFi 등록 + provider WifiSettings</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="16">
         <f>IF(F17="✅",1,IF(F17="🔄",0.5,IF(F17="◑",0.7,IF(F17="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H17" s="13" t="inlineStr"/>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="H17" s="17" t="inlineStr"/>
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>2026-07-초</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr">
-        <is>
-          <t>C10·C13 해소</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="n"/>
+      <c r="J17" s="18" t="inlineStr"/>
+      <c r="K17" s="18" t="inlineStr"/>
+      <c r="L17" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>P16</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>mobile WiFi 클라이언트</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>mobile</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>비콘→WiFi 묶음 fetch·캐시 + BSSID 검증 + 손님 자동/승인 + home 보강</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>비콘→WiFi 묶음 fetch + BSSID 검증</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="16">
         <f>IF(F18="✅",1,IF(F18="🔄",0.5,IF(F18="◑",0.7,IF(F18="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="H18" s="17" t="inlineStr"/>
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>2026-07-초</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr"/>
-      <c r="K18" s="14" t="inlineStr"/>
-      <c r="L18" s="10" t="n"/>
+      <c r="J18" s="18" t="inlineStr"/>
+      <c r="K18" s="18" t="inlineStr"/>
+      <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>P17</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>.mobileconfig 다건 설치</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>.mobileconfig 다건</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>BE·mobile·iOS</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>.mobileconfig 생성·다건 설치 (서명은 인증서 도착 후)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>.mobileconfig 생성·다건 설치</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="16">
         <f>IF(F19="✅",1,IF(F19="🔄",0.5,IF(F19="◑",0.7,IF(F19="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H19" s="13" t="inlineStr"/>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="H19" s="17" t="inlineStr"/>
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr"/>
-      <c r="K19" s="14" t="inlineStr">
-        <is>
-          <t>서명은 Apple 인증서 확보 후 적용</t>
-        </is>
-      </c>
-      <c r="L19" s="10" t="n"/>
+      <c r="J19" s="18" t="inlineStr"/>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>서명은 인증서 후</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>P18</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>credential_mode managed</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>BE·provider·mobile</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>비번 교체 리마인드 + 인가 손님 자동 전파</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="16">
         <f>IF(F20="✅",1,IF(F20="🔄",0.5,IF(F20="◑",0.7,IF(F20="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H20" s="13" t="inlineStr"/>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="H20" s="17" t="inlineStr"/>
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr"/>
-      <c r="K20" s="14" t="inlineStr">
-        <is>
-          <t>v1 flag — 코드만 완성, UI 비공개</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="n"/>
+      <c r="J20" s="18" t="inlineStr"/>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>v1 flag 비공개</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>P19</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>WiFi 로밍 B</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>units/grant 관리 화면</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>units/grant 관리</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>admin·provider·BE</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>호실·자리 시간제 권한 관리 UI</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>호실·자리 시간제 권한 UI</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="16">
         <f>IF(F21="✅",1,IF(F21="🔄",0.5,IF(F21="◑",0.7,IF(F21="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H21" s="13" t="inlineStr"/>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="H21" s="17" t="inlineStr"/>
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr"/>
-      <c r="K21" s="14" t="inlineStr">
-        <is>
-          <t>v1 flag — 코드만 완성, UI 비공개</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="n"/>
+      <c r="J21" s="18" t="inlineStr"/>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>v1 flag 비공개</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>P20</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>심의 마무리</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>앱 버전관리</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>admin·mobile</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>admin app-versions UI(BE 완성) + mobile OS 최소버전 게이트</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>admin app-versions UI + mobile OS 최소버전 게이트</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="16">
         <f>IF(F22="✅",1,IF(F22="🔄",0.5,IF(F22="◑",0.7,IF(F22="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H22" s="13" t="inlineStr"/>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="H22" s="17" t="inlineStr"/>
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr"/>
-      <c r="K22" s="14" t="inlineStr"/>
-      <c r="L22" s="10" t="n"/>
+      <c r="J22" s="18" t="inlineStr"/>
+      <c r="K22" s="18" t="inlineStr"/>
+      <c r="L22" s="12" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>P21</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>심의 마무리</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>심의 메타 자산</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>mobile·iOS</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>PrivacyInfo.xcprivacy + Bundle ID 확정 + Android Photo Picker + 계정삭제 웹 URL</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>PrivacyInfo.xcprivacy + Bundle ID + Photo Picker</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="16">
         <f>IF(F23="✅",1,IF(F23="🔄",0.5,IF(F23="◑",0.7,IF(F23="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="H23" s="17" t="inlineStr"/>
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr"/>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>심의 reject 방지 필수</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="n"/>
+      <c r="J23" s="18" t="inlineStr"/>
+      <c r="K23" s="18" t="inlineStr"/>
+      <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>P22</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>회원 QR 운영</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>쿠폰·스탬프 회원 QR</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>mobile·provider·BE</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>회원 QR(URL 토큰) + provider 스캔/코드입력 → 적립·사용 + 친구초대 QR/링크</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>회원 QR + provider 스캔/코드입력 + 친구초대 QR</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="16">
         <f>IF(F24="✅",1,IF(F24="🔄",0.5,IF(F24="◑",0.7,IF(F24="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H24" s="13" t="inlineStr"/>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="H24" s="17" t="inlineStr"/>
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>2026-07-초~중</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr"/>
-      <c r="K24" s="14" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr"/>
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>P9 이후 병행</t>
         </is>
       </c>
-      <c r="L24" s="10" t="n"/>
+      <c r="L24" s="12" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1991,20 +3244,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2035,200 +3288,281 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>이전 작업 (~Phase 0)</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>PR #1~#51 + 디자인 통합 + 51 PR 머지</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>~수개월</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>완료 — 코드 측면 출시 직전</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Phase 0 전수 감사</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>갭 리스트 14 Critical + High 발굴</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>~1일</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 인프라</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>P1~P3</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>~4일</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>5월 말</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Critical 도메인</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 Critical</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>P4~P13 (10 PR)</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>~2주</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>6월 중순</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
-        <is>
-          <t>P4~P8 완료, 나머지 진행 예정</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>WiFi 로밍 (B 풀스코프)</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-중</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>P4~P8 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 WiFi 로밍 B</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>P14~P19 (6 PR)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>~2.5~3주</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>7월 초~중순</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>feature flag로 P18·P19 v1 비공개</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>쿠폰·스탬프 회원 QR</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-초~중</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>feature flag</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 회원 QR</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>P22 (P9 이후 병행)</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>~1주</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>7월 초~중순</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>심의 마무리</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-초~중</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 심의 마무리</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>P20~P21</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>~3일</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>7월 중순</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-중</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Phase 2~4 테스트·시드</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>테스트데이터 시드 + 페르소나 검증</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>6 페르소나 + 시나리오 검증</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>~1.5주</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>7월 중순~하순</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-중~하순</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Phase 5 제출 준비</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>빌드 + 스토어 메타데이터</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>며칠</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>7월 하순</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-하순</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>출시</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>앱스토어/플레이 공개</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>앱스토어/Play 공개</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>7월 하순~8월 초</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr"/>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-하순~8월 초</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>외부 서비스 신청 시작</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>법인카드 수취 후 일괄 신청</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>~1주 (심사 1~2주)</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-02 주</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>카카오·솔라피·토스 심사 병행</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/exports/pathwave_dev_checklist.xlsx
+++ b/docs/exports/pathwave_dev_checklist.xlsx
@@ -70,7 +70,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -89,22 +89,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDD7EE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -139,19 +134,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -166,12 +161,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -179,6 +168,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -771,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -847,12 +839,12 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>PR #1~#5, #28, #45, #55</t>
+          <t>BE — 이메일 인증·가입</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>이메일 가입·로그인, 5종 소셜 로그인(Google/Apple/Facebook/Kakao/Naver), 동의 단계, 미성년자 보호, 회원 탈퇴 흐름</t>
+          <t>/api/auth send-code·verify-code·register·login, email_codes 테이블, bcrypt, JWT</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
@@ -860,11 +852,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>코드 완료, 실 키는 서비스 가입 후</t>
-        </is>
-      </c>
+      <c r="F4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -872,19 +860,19 @@
           <t>인증/회원가입</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>BE — 5종 소셜 로그인</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>dev 인증 우회 제거 + 실 로그인폼 복구 + /forgot-password 정식 구현</t>
+          <t>/api/auth/social/{google,apple,facebook,kakao,naver}, Firebase 토큰 검증, 동의 처리</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -894,7 +882,7 @@
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>BE 2 API + provider 페이지</t>
+          <t>실 키는 카카오·네이버 검수 후</t>
         </is>
       </c>
     </row>
@@ -904,36 +892,32 @@
           <t>인증/회원가입</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>남은</t>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>실 키 검증</t>
+          <t>BE — 동의·약관·미성년자</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Firebase·카카오·네이버 실 키로 통합 테스트 (서비스 가입 후)</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>외부 서비스 활성화 후</t>
-        </is>
-      </c>
+          <t>8 KIND 정책 등록, record_consents 감사 로그, parent_invite 코드 발급</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>매장 정보</t>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -943,12 +927,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>PR #2, #14, #16</t>
+          <t>BE — 회원 탈퇴 + 14일 그레이스</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>매장 CRUD, 이미지 갤러리, 다국어 번역 캐시</t>
+          <t>/api/auth/delete-account, soft delete, deleted_at, 14일 후 재가입</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -961,22 +945,22 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>매장 정보</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>BE — 모바일 비밀번호 재설정</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>StoreInfo 하드코딩 제거 + StoreService 실연동 + PwFooter + dead code 정리</t>
+          <t>/api/auth/forgot-password·reset-password (users 테이블 전용)</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -984,48 +968,40 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>백엔드 schema 부재(category/holidays) → P8c 별도 작업</t>
-        </is>
-      </c>
+      <c r="F8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>매장 정보</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>남은</t>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>P8c (별도 작업 칩)</t>
+          <t>BE — 시설 계정 가입·로그인</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>facilities 스키마 category/holidays/detailAddress 컬럼 추가 또는 UI 정리</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>결정 필요</t>
-        </is>
-      </c>
+          <t>/api/facility/send-code·register·login, facility_accounts, 운영자 승인 대기</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>결제·구독</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
@@ -1035,12 +1011,12 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>PR #39, #41, #43~46, #56</t>
+          <t>mobile — 가입 5단계</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>billing API 전체(cards/subscriptions/payments/refund/extend), PG provider 추상화</t>
+          <t>consent → 본인인증 → 이메일/소셜 → 약관 동의 → 완료</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1048,31 +1024,27 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>백엔드 sim 모드 — 토스 키 활성화 시 운영</t>
-        </is>
-      </c>
+      <c r="F10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>결제·구독</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>mobile — 로그인/비번 재설정 UI</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>provider 카드 평문저장 제거(PCI) + BillingService + Payment/Subscription/ServiceRequest 실연동</t>
+          <t>login_screen, forgot_password_screen (2단계)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1080,63 +1052,59 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>admin Payments는 이미 정합</t>
-        </is>
-      </c>
+      <c r="F11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>결제·구독</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>남은</t>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>토스 키 활성화</t>
+          <t>provider — 회원가입·로그인 UI</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>토스페이먼츠 가맹점 심사 통과 후 PG_PROVIDER=toss + 실 결제 검증</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>실제 폼·소셜로그인·매장 정보 입력</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>외부(심사 1~2주)</t>
+          <t>폼은 dev 우회로 가려졌었음 → P4에서 복구</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>쿠폰·스탬프</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>PR #6, #18, #22, #29</t>
+          <t>P4 — provider dev 우회 제거</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>쿠폰 발행/사용/만료, 스탬프 적립/리워드, 정책 설정</t>
+          <t>DEV_AUTO_LOGIN을 import.meta.env.DEV 게이트, Login 자동토큰 useEffect 제거, Signup 게스트 게이트</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -1144,72 +1112,80 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>출시 빌드에서 실 로그인폼 노출</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>쿠폰·스탬프</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P4 — 시설 비번 재설정 신규</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>provider Coupons·Stamps mock→실연동 + mobile 쿠폰 사용 silent error 수정</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr"/>
+          <t>BE /api/facility/forgot-password·reset-password 신규 + provider ForgotPassword 페이지·라우트</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>갭리스트 오기: 파일 없었음</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>쿠폰·스탬프</t>
+          <t>인증/회원가입</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>Phase 1</t>
+          <t>남은</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>P22</t>
+          <t>실 키 검증</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>회원 QR (URL 토큰 인코딩) + provider 스캔/코드입력 → 적립/사용 + 친구초대 QR/링크</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
+          <t>카카오·네이버 검수 완료 후 실 소셜 로그인 통합 테스트</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>P9 이후 병행</t>
+          <t>외부 서비스 활성화 후</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>매장 정보</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
@@ -1219,12 +1195,12 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>PR #16, #21, #142</t>
+          <t>BE — 매장 CRUD</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>1:1 채팅 rooms/messages, SSE 스트림, 신고/차단</t>
+          <t>/api/facilities CRUD + 이미지 갤러리 + 다국어 번역 캐시</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -1237,71 +1213,63 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>채팅</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>P8 (◑)</t>
+          <t>admin — 매장 관리</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>provider CustomerChat 실연동 + admin ChatMonitor + BE /api/chat/reports + mobile SSE 재연결</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>◑</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>⚠ app.py 재시작 후 활성</t>
-        </is>
-      </c>
+          <t>admin Stores 페이지, 비콘 매핑, 번역 등록</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>채팅</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>남은</t>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>P8b</t>
+          <t>mobile — 매장 상세 화면</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>채팅 자동 번역(번역 캐시 스키마 + 뷰어별 언어 + translator 연결)</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>DeepL/Google Translate 키 확보 후</t>
-        </is>
-      </c>
+          <t>facility_screen (이미지/영업시간/주소/채팅 진입)</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>알림 (Inbox + Push)</t>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
@@ -1311,12 +1279,12 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>PR #38, #44, #50</t>
+          <t>provider — StoreInfo UI 골격</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Inbox·Announcements, FCM 푸시, APNs(HTTP/2 JWT), 알림 선호 카테고리</t>
+          <t>편집/저장/지도/이미지 업로드/비콘 claim — UI 완성, 데이터는 mock</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -1324,160 +1292,160 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>데이터 연동은 P5</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>알림 (Inbox + Push)</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P5 — provider StoreInfo 실연동</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>provider Notifications 실연동 + mobile 알림 라우팅 + 알림 탭 보강</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
+          <t>하드코딩 제거 → StoreService.list/update PATCH 실 연동, 실 fid로 비콘 claim</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>P5 — Settings 푸터 → PwFooter</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>하드코딩 회사정보 제거 → CompanyInfoService 실 법인정보</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>P5 — dead code 정리</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Facilities.jsx (1계정1매장 정책 위반 + 라우트 미연결) 삭제</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>P8c — 스키마 갭</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>facilities 테이블에 category/holidays/detailAddress 컬럼 추가 또는 UI 정리 (현재 비영속)</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>WiFi (1회 연결)</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>PR #11, #49</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>wifi_profiles 기본, native plugin(iOS/Android) 자동 가입 요청, BLE 핸드셰이크</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>1회 연결만, 로밍 미지원</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>WiFi 로밍 (B 풀스코프)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>P14~P19</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>wifi_profiles 확장 + beacon_wifi·units·grant·devices + admin/provider 등록 + mobile 클라이언트 + .mobileconfig 다건 + managed/units (flag)</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>6월 말~7월 중</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>비콘 (인벤토리/claim/모니터)</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>PR #37, #38</t>
-        </is>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>admin 인벤토리 CSV 입고, provider claim, 배터리 모니터링, 펌웨어 표시</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>별도 작업 칩 등록됨</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>비콘</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>P15 (병합)</t>
+          <t>BE — billing API 전체</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>beacons.role(wifi/cashier) 추가 + admin·provider UI</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>/api/billing cards·subscriptions·payments·refund·extend·receipt-email + PG provider 추상화(sim/toss)</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>i18n (12언어)</t>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -1487,12 +1455,12 @@
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>BE translations API + admin CRUD</t>
+          <t>admin — Payments + Subscriptions</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>백엔드 translations 테이블, DeepL 통합, 12개 supportedLocales, admin CRUD</t>
+          <t>adminApi.listPayments/listSubscriptions/refundPayment 실연동 + 환불 모달</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -1500,27 +1468,31 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr"/>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>이미 정합 — P7에서 변경 없음</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>i18n</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>provider — PaymentManagement·Subscriptions UI 골격</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>mobile I18nService DB 통일 + 전 화면 t() 전환 + ko 시드 550 + DeepL 일괄번역 스크립트</t>
+          <t>다단계 결제 흐름/카드 입력 모달/구독 카드 UI 완성, 데이터는 mock + localStorage</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -1530,61 +1502,57 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>11개 언어 번역 = DeepL 키 확보 후 batch 실행</t>
+          <t>데이터 연동은 P7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>i18n</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>남은</t>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>DeepL 번역 batch</t>
+          <t>P7 — BillingService 신규</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>translations DB의 ko 키 → 11개 언어 자동 번역(약 22 × 549건)</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>DeepL API 키 활성화 후</t>
-        </is>
-      </c>
+          <t>provider /api/billing 래퍼 (cards/subscriptions/payments/receipt-email), PCI 주석</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>정책/약관</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>8종 KIND 등록</t>
+          <t>P7 — 카드 평문저장 제거 (C6)</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>terms, privacy, location, marketing, push, camera, storage, third_party, age14 DB 등록</t>
+          <t>localStorage pathwave_payment_card + audit 큐 완전 제거, registerCard(brand, last4)만 전송</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -1592,83 +1560,91 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr"/>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>PCI 준수, 전체 PAN/CVC 미전송</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>정책/약관</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P7 — Payment/Subscription/ServiceRequest 실연동</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>환불·청소년·쿠키 정책 3종 BE/admin/노출 추가 + policy_view 언어 정합</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
+          <t>모든 MOCK_* 제거, 결제 흐름을 PaymentManagement/ServiceRequest 모두 동일 백엔드로 통합</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>토스 키 활성화</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>토스페이먼츠 심사 통과 후 PG_PROVIDER=toss + 실 결제 end-to-end 검증</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F29" s="12" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>디자인 시스템</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
-        <is>
-          <t>3콘솔 디자인 정합</t>
-        </is>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>mobile dark + 보라, provider-web dark + 녹색, admin-web dark + 블루 — 3콘솔 디자인 토큰 통일</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr"/>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>외부 심사 1~2주</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>디자인 시스템</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>쿠폰</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>P1·P3</t>
+          <t>BE — 쿠폰 발행/사용/만료</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>mobile 테마 단일화 + 시스템 폰트 + Pw* 위젯 / 웹 alert·confirm 33곳 → 공용 모달</t>
+          <t>/api/coupons issue/use/expire, 정책 설정, 통계</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
@@ -1679,9 +1655,9 @@
       <c r="F31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>슈퍼어드민 (admin-web)</t>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -1691,12 +1667,12 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>PR #36~#39, #142</t>
+          <t>mobile — 쿠폰함 화면</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Login + Dashboard + Beacons + Approvals + Battery + Announcements + Payments + Subscriptions + Policies + Reports + Translations + Audit</t>
+          <t>coupons_screen (active/used/expired 탭), 사용 다이얼로그</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
@@ -1704,40 +1680,48 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr"/>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>쿠폰 사용 silent error 잔존 → P9에서 수정</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>쿠폰</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>P11·P20</t>
+          <t>provider — Coupons·CouponForm UI</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Dashboard 가짜데이터 제거 + StaffMonitor·CouponStats placeholder 해소 + app-versions UI(BE 완성)</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="F33" s="12" t="inlineStr"/>
+          <t>쿠폰 목록·생성·통계 UI 완성, 데이터는 mock</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>데이터 연동은 P9</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>직원 관리</t>
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -1747,12 +1731,12 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>백엔드 staff API</t>
+          <t>admin — 쿠폰 통계</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>직원 초대/권한/관리 백엔드</t>
+          <t>admin abuse·coupon stats</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -1760,30 +1744,34 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr"/>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>CouponStats placeholder 일부 → P11</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>직원 관리</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+          <t>쿠폰</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P9 — provider Coupons 실연동</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>provider StaffManagement 실연동 + admin StaffMonitor 실연동</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
+          <t>mock→/api/coupons 실연동, 쿠폰 발행/회수 정상 흐름</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
@@ -1791,88 +1779,84 @@
       <c r="F35" s="12" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>심의 직격 (mobile)</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>쿠폰</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P9 — mobile 쿠폰 사용 silent error</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>consent placeholder 제거 + 동의 로드 실패 복구 + settings dev 정보 제거 + 앱 버전 동적화</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
+          <t>사용 실패 시 사용자 피드백 + 목록 갱신</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>심의 reject 방지</t>
-        </is>
-      </c>
+      <c r="F36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>심의 메타 자산</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>쿠폰</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>P21</t>
+          <t>P22 — 회원 QR 사용 흐름</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>PrivacyInfo.xcprivacy + Bundle ID 확정 + Android Photo Picker + 계정삭제 웹 URL</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
+          <t>손님 마이페이지 QR → provider 스캔/코드입력 → 적립·사용</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>iOS/Android 심사 필수</t>
+          <t>P9 이후 병행</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>OCR 허위 제거</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
+          <t>스탬프</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>BE — 스탬프 적립/리워드</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>WifiSettings·ServiceRequest runOcrMock 제거 → 정직한 수동입력 UI</t>
+          <t>/api/stamps accrue/list, 시설별 정책, BLE 비콘 감지 자동 적립</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -1880,135 +1864,2679 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>스탬프</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>mobile — 스탬프 화면</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>stamps_screen (시설별 카드, 진행률, 보상)</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>스탬프</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>provider — Stamps·StampForm UI</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>스탬프 정책·통계 UI 완성, 데이터는 mock</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>데이터 연동은 P9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>스탬프</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>P9 — provider Stamps 실연동</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>mock→/api/stamps 실연동</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>스탬프</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>P22 — 수동 적립(staff 모드)</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>회원 QR 스캔 → 스탬프 수동 적립 (auto/staff 모드 선택)</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>BE — chat 전체 API</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>/api/chat rooms·messages·SSE 스트림·read + chat_blocks 테이블 + is_blocked 가드</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>BE — abuse_reports + chat_blocks</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>/api/abuse-reports + /api/admin/abuse-reports + /api/blocks</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>mobile — 채팅 화면</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>chat_list_screen + chat_detail_screen (SSE 실시간) + 신고/차단 메뉴 + 가이드라인 모달</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>재연결 미지원이었음 → P8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>provider — CustomerChat UI</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>대화창 UI 완성, 데이터는 DUMMY_CHATS 7개 더미</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>데이터 연동은 P8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>provider — ChatService 메서드</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>openRoom/listRooms/listMessages/sendMessage/markRead/subscribe(SSE) 다 작성됨</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>호출만 안 되고 있었음</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>admin — ChatMonitor UI</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>신고 큐 테이블 UI 완성, /api/chat/reports 호출(없는 엔드포인트) → placeholder</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>BE 엔드포인트만 필요 — P8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>P8 — provider CustomerChat 실연동</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>DUMMY 제거 → ChatService 5종 호출, 30초 폴링 + 낙관적 전송 + SSE 정리</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>P8 — admin /api/chat/reports BE</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>abuse_reports → 신고 큐 변환 (room_name·reason·reporter·status), super_admin 가드</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>ChatMonitor UI 무변경, 데이터만 실 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>P8 — mobile SSE 끊김 재연결</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>StreamController 기반 재작성, 지수 backoff(1→30s), ?after_id=로 누락 보충</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>⚠ app.py 재시작 후 활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>남은 — P8b</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>번역 캐시 스키마</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>chat_messages 또는 별도 번역 캐시 테이블 (message_id, lang → translated_text)</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>남은 — P8b</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>뷰어별 언어 번역 + translator 연결</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>list_messages·SSE 응답에 ?lang= 기준 번역 포함, translator.py 통합</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>DeepL/Google Translate 키 활성화 후 — USP 기능</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>알림 (Inbox + Push)</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>BE — 알림 API</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>/api/notifications inbox·announcements·read + notification_preferences (카테고리별)</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>알림 (Inbox + Push)</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>BE — FCM + APNs</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>FCM (firebase-admin) + APNs (HTTP/2 JWT ES256) + multi-platform 라우팅</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>실 키는 Firebase 활성화 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>알림 (Inbox + Push)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>mobile — 알림 화면 + 권한 동의</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>notifications_screen (인박스/공지 탭) + notification_permission_dialog</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>라우팅 보강 필요 → P10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>알림 (Inbox + Push)</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>provider — Notifications UI</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>받은 알림 + 시스템 공지 UI 완성, 데이터는 mockInbox 14건</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>데이터 연동은 P10</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>알림 (Inbox + Push)</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>admin — 공지 CRUD + 발송</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>admin Announcements CRUD + 실 푸시 발송 통합</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>알림 (Inbox + Push)</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>P10 — provider Notifications 실연동</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>mockInbox 제거 → 실 /api/notifications 연동</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>알림 (Inbox + Push)</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>P10 — mobile 알림 라우팅</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>알림 종류별 화면 이동 (coupon→쿠폰함, chat→채팅 등)</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>WiFi (1회 연결)</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>BE — wifi_profiles + handshake</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>/api/beacon/wifi handshake (LIMIT 1 단일 반환) + wifi_profiles 기본 스키마</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>로밍은 LIMIT 1 → 묶음 반환으로 확장 필요(P15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>WiFi (1회 연결)</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>mobile — native plugin</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>iOS NEHotspotConfiguration + Android WifiNetworkSuggestion (자동 가입 요청)</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>1회 연결만, 로밍 미지원</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>WiFi (1회 연결)</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>mobile — WifiConnectScreen</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>BLE 핸드셰이크 → WiFi 정보 전달 + OS 자동 가입 트리거</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>WiFi (1회 연결)</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>provider — WifiSettings UI</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>WiFi 등록·수정·비활성 UI 완성, 사진 첨부 + 가짜 OCR 자동입력</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="inlineStr">
+        <is>
+          <t>OCR 허위는 P6에서 제거됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>WiFi 로밍 (B)</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>P14 — 데이터 모델 재설계</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>wifi_profiles 확장 + beacon_wifi·units·wifi_access_grant·devices 신규 + beacons.role(wifi/cashier)</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>6월 말~7월 초</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>WiFi 로밍 (B)</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>P15 — WiFi 등록·연동</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>handshake 묶음 반환(LIMIT 1 제거) + admin WiFi 등록화면 신규 + provider WifiSettings 실연동 + 비콘 role UI</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F66" s="12" t="inlineStr">
+        <is>
+          <t>C10·C13 해소</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>WiFi 로밍 (B)</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>P16 — mobile WiFi 클라이언트</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>비콘→WiFi 묶음 fetch·캐시 + BSSID 검증 + "WiFi 변경됨" 흐름 + 손님 자동/승인 + home 진입점</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>WiFi 로밍 (B)</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>P17 — .mobileconfig 다건</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>.mobileconfig 생성·다건 설치 (서명은 Apple 인증서 확보 후 적용)</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F68" s="12" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>WiFi 로밍 (B)</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>P18 — credential_mode managed</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>비번 교체 리마인드 + 인가 손님 자동 전파 + 알림 연동</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>v1 flag 비공개 (코드만 완성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>WiFi 로밍 (B)</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>P19 — units/grant 관리</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>호실·자리 시간제 권한 관리 UI (admin/provider)</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="inlineStr">
+        <is>
+          <t>v1 flag 비공개</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>비콘 (인벤토리/claim/모니터)</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>BE — beacons lifecycle</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>beacons 테이블 inventory→active→inactive/lost, claim API</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>비콘 (인벤토리/claim/모니터)</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>admin — Beacons UI</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>인벤토리 CSV 입고, claim 모니터, 배터리·펌웨어 표시</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>비콘 (인벤토리/claim/모니터)</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>provider — 비콘 claim 흐름</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>StoreInfo 내 비콘 claim UI + listBeacons</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>실 fid는 P5에서 해소</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>비콘 (인벤토리/claim/모니터)</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>P15 (병합)</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>beacons.role(wifi/cashier) 컬럼 추가 + admin·provider UI</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>i18n (12언어)</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>BE — translations API</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>translations 테이블, GET /api/i18n/{lang}, DeepL 통합 모듈, admin CRUD UI</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>i18n (12언어)</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>admin — i18n CRUD</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>키별 다국어 입력·수정·자동번역 트리거</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>i18n (12언어)</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>mobile — supportedLocales 7개</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>7개 언어 기본 + 일부 화면만 i18n 적용 (대부분 한글 하드코딩)</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>12개로 확장 + 전 화면 → P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>i18n (12언어)</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>P2 — mobile I18nService DB 통일</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>12 supportedLocales, 전 화면·위젯 t() 전환, ko 시드 203→550</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>i18n (12언어)</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>P2 — DeepL 일괄번역 스크립트</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>translate_i18n_deepl.py 작성 — 키 활성화 시 22언어×549건 배치</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>키 활성화 후 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>i18n (12언어)</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>11개 언어 batch 번역</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>DeepL API 키 활성화 후 batch 실행 (현재 ko만)</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>DeepL 키 활성화 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>BE — policies API + 8 KIND</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>terms·privacy·location·marketing·push·camera·storage·third_party·age14 등록·버전관리</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>mobile/provider — policy_view 화면</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>약관 본문 노출, 푸터·설정·동의 흐름에서 진입</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="inlineStr">
+        <is>
+          <t>?lang=ko 강제 문제 잔존 → P13</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>admin — Policies CRUD</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>약관 등록·버전 발행 UI</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>P13 — 환불·청소년·쿠키 3종</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>BE policy KIND 추가 + admin Policies + mobile/provider 노출 + policy_view 언어 정합</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F84" s="12" t="inlineStr">
+        <is>
+          <t>C14 해소</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>mobile — PwTheme 다크 + 보라</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>PwTheme + 13종 Pw* 위젯 (Radio·Checkbox·Dropdown·Chip 4종은 P1에서 추가)</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>provider-web — 다크 + 녹색</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>provider 디자인 시스템 통합 PR #66~#87 (게스트 진입 포함)</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="inlineStr">
+        <is>
+          <t>게스트 진입은 P4에서 dev 게이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>admin-web — 다크 + 블루</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>admin 다크 톤 통합 PR #65</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>P1 — mobile 기반 단일화</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>테마 단일화(AppTheme+NeuTheme→1) + 시스템 폰트 + neu/ 위젯 통합 + Pw* 4종 신규</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>P3 — 웹 alert/confirm → 공용 모달</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>provider 16곳 + admin 17곳의 네이티브 alert/confirm → useDialog() 비동기 모달, 색 토큰 정합(보라 잔존 2곳→녹색)</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>admin — 기본 7페이지</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>Login + Dashboard + Beacons + Approvals + Battery + Announcements + Stores</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="inlineStr">
+        <is>
+          <t>PR #36~#38</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>admin — Payments + Subscriptions + 환불</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>결제/구독 관리 + 환불 모달 — 실 API 연동 완료</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>PR #39</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>admin — Policies + Translations + Audit + Reports</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>약관·번역·감사 로그·신고 관리</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>admin — 채팅 신고/차단 (PR #142)</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>abuse_reports admin 처리 + chat_blocks</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>/api/chat/reports 변환만 P8에서 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>P11 — Dashboard 가짜데이터 제거</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>실 통계 API 연동</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>P11 — StaffMonitor·CouponStats placeholder</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>실 데이터 연동</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F95" s="12" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>P20 — app-versions UI</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>백엔드 routes/version.py 완성 — admin UI만 신규</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>C11 해소</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>BE — staff API</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>직원 초대/권한/관리 백엔드</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F97" s="12" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>provider — StaffManagement UI</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>직원 목록·초대·권한 UI 완성, 데이터는 mock</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>데이터 연동은 P11</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>mobile — MemberProfile UI</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>회원 프로필 mock UI</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F99" s="12" t="inlineStr">
+        <is>
+          <t>mobile 직원 기능은 v1 비공개</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>P11 — provider StaffManagement 실연동</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>mock→실 staff API 연동</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>P11 — admin StaffMonitor 실연동</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>시설별 직원 모니터링</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>mobile 심의 직격</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>consent 단계</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>8 KIND 동의 + 미성년자 보호 + 약관 본문</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>placeholder 노출 버그 존재 → P12</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>mobile 심의 직격</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>settings 화면</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>계정·알림·약관·고객지원·회원탈퇴</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>dev API URL 노출 + 앱 버전 하드코딩 → P12</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>mobile 심의 직격</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>P12 — consent placeholder 제거</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>⚠ placeholder 본문 노출 버그 수정</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
         <is>
           <t>심의 reject 방지</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>mobile 심의 직격</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>P12 — 동의 로드 실패 dead-end 복구</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>네트워크 오류 시 재시도/안내</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F105" s="12" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>mobile 심의 직격</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>P12 — settings dev 정보 제거 + 앱 버전 동적</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>API URL 노출 제거 + package_info_plus로 버전 동적화</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>C9 해소</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>앱 버전관리</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>BE — routes/version.py + app_versions 테이블</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>admin GET/PUT /api/admin/app-versions, mobile GET /api/version</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr">
+        <is>
+          <t>코드 완성 — admin UI만 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>앱 버전관리</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>P20 — admin app-versions UI</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>버전 등록·강제업데이트/권장 토글·OS별</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>앱 버전관리</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>P20 — mobile OS 최소버전 게이트</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>splash에서 버전 체크 → 강제 업데이트 모달</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F109" s="12" t="inlineStr">
+        <is>
+          <t>splash 화면 ⏰ 처리 일부 존재</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>심의 메타 자산</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>동의 흐름·약관 노출</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>8 KIND + 미성년자 + UGC 가이드라인 (채팅)</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>심의 reject 방지 대부분 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>심의 메타 자산</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>P21 — iOS PrivacyInfo.xcprivacy</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>iOS 17.4+ 필수 — 데이터 수집/추적 명시</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F111" s="12" t="inlineStr">
+        <is>
+          <t>심의 reject 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>심의 메타 자산</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>P21 — Bundle ID 확정</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>co.triggersoft.pathwave 등 최종 결정</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>심의 메타 자산</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>P21 — Android Photo Picker</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Android 13+ 신규 권한 모델 적용</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>심의 메타 자산</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>P21 — 계정삭제 웹 URL</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Google Play 정책 — 앱 외부 웹에서도 계정 삭제 가능 URL 제공</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>runOcrMock (가짜)</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>WifiSettings·ServiceRequest 사진 선택 시 랜덤 가짜 ID/PW 자동입력 — 심의 reject 위험</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>P6에서 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>P6 — OCR 허위 제거</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>runOcrMock 삭제 → 정직한 수동입력 UI, 사진은 참고 첨부로 재정의</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>C5 해소</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>회사 정보 (footer)</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>P5 (포함)</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>Settings 푸터 → PwFooter (CompanyInfoService → 트리거소프트 실 법인정보)</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>법인 등기 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>BE — company_info API (Phase M)</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>슈퍼어드민 입력값 GET /api/company-info</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>회사 정보 (footer)</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>mobile/provider PwFooter</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>CompanyInfoService 실연동 — DB값 + i18n fallback</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>회사 정보 (footer)</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>P5 — Settings 푸터 통일</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>provider Settings 하드코딩 푸터 → PwFooter</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>회사 정보 (footer)</t>
+        </is>
+      </c>
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>실 법인정보 입력</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>슈퍼어드민이 트리거소프트 실 정보(법인등록번호 등) admin에서 입력</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>법인 등기 완료 — 등록만 남음</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>운영 인프라</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>PR #35, #41, #51</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>SECRET_KEY/AES_KEY ENV + CORS 화이트리스트 + rate-limit + gunicorn/wsgi + Sentry + PostgreSQL 어댑터</t>
-        </is>
-      </c>
-      <c r="E40" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>실 호스팅은 외부 서비스 활성화 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>BE — 보안 강화</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>SECRET_KEY/AES_KEY ENV 강제 + CORS 화이트리스트 + rate-limit (PR #35)</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>BE — provider 추상화</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>PG provider(sim/toss) + Email provider(stub/sendgrid/smtp) + Push provider(stub/fcm/apns)</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>키 활성화 시 즉시 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>BE — gunicorn/wsgi + Sentry</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>프로덕션 배포 골격 + Sentry 통합</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F123" s="12" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>BE — PostgreSQL 어댑터</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>DATABASE_URL ENV 자동 분기 (sqlite ↔ pg 호환)</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>실 호스팅 배포</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>AWS/Render/Railway 중 선택 + 실 도메인 + Postgres + 환경변수 키 주입</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>외부 서비스 활성화 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
         <is>
           <t>Phase 2~4 테스트</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B126" s="13" t="inlineStr">
         <is>
           <t>남은</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>W7 테스트 시드</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>6 페르소나(외국인/한국인/소규모/중대형/직원/슈퍼어드민) 테스트 데이터 시드 + 시나리오 검증</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>W7 — 6 페르소나 테스트 시드</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>외국인/한국인/소규모/중대형/직원/슈퍼어드민 시나리오 데이터 + walk-through 검증</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F41" s="12" t="inlineStr">
+      <c r="F126" s="12" t="inlineStr">
         <is>
           <t>7월 중순~하순</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
         <is>
           <t>Phase 5 제출</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B127" s="13" t="inlineStr">
         <is>
           <t>남은</t>
         </is>
       </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>스토어 제출</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>iOS/Android 빌드 + 스토어 메타데이터 + 스크린샷 + 심의 제출</t>
-        </is>
-      </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>스토어 메타데이터 + 빌드</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>iOS/Android 빌드 + 스크린샷 + 메타데이터(다국어) + 심의 제출</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="F42" s="12" t="inlineStr">
+      <c r="F127" s="12" t="inlineStr">
         <is>
           <t>7월 하순~8월 초</t>
         </is>
@@ -2138,26 +4666,26 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="14">
         <f>IF(F2="✅",1,IF(F2="🔄",0.5,IF(F2="◑",0.7,IF(F2="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I2" s="18" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J2" s="18" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K2" s="18" t="inlineStr"/>
+      <c r="K2" s="16" t="inlineStr"/>
       <c r="L2" s="12" t="n"/>
     </row>
     <row r="3">
@@ -2191,26 +4719,26 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="14">
         <f>IF(F3="✅",1,IF(F3="🔄",0.5,IF(F3="◑",0.7,IF(F3="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K3" s="18" t="inlineStr"/>
+      <c r="K3" s="16" t="inlineStr"/>
       <c r="L3" s="12" t="n"/>
     </row>
     <row r="4">
@@ -2244,26 +4772,26 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="14">
         <f>IF(F4="✅",1,IF(F4="🔄",0.5,IF(F4="◑",0.7,IF(F4="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I4" s="18" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K4" s="18" t="inlineStr"/>
+      <c r="K4" s="16" t="inlineStr"/>
       <c r="L4" s="12" t="n"/>
     </row>
     <row r="5">
@@ -2297,26 +4825,26 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="14">
         <f>IF(F5="✅",1,IF(F5="🔄",0.5,IF(F5="◑",0.7,IF(F5="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K5" s="18" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>⚠ app.py 재시작 필요</t>
         </is>
@@ -2354,26 +4882,26 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="14">
         <f>IF(F6="✅",1,IF(F6="🔄",0.5,IF(F6="◑",0.7,IF(F6="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K6" s="18" t="inlineStr"/>
+      <c r="K6" s="16" t="inlineStr"/>
       <c r="L6" s="12" t="n"/>
     </row>
     <row r="7">
@@ -2407,26 +4935,26 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="14">
         <f>IF(F7="✅",1,IF(F7="🔄",0.5,IF(F7="◑",0.7,IF(F7="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I7" s="18" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K7" s="18" t="inlineStr"/>
+      <c r="K7" s="16" t="inlineStr"/>
       <c r="L7" s="12" t="n"/>
     </row>
     <row r="8">
@@ -2460,26 +4988,26 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="14">
         <f>IF(F8="✅",1,IF(F8="🔄",0.5,IF(F8="◑",0.7,IF(F8="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K8" s="18" t="inlineStr"/>
+      <c r="K8" s="16" t="inlineStr"/>
       <c r="L8" s="12" t="n"/>
     </row>
     <row r="9">
@@ -2508,31 +5036,31 @@
           <t>provider CustomerChat + admin ChatMonitor + BE 신고 API + mobile SSE 재연결</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>◑</t>
         </is>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="14">
         <f>IF(F9="✅",1,IF(F9="🔄",0.5,IF(F9="◑",0.7,IF(F9="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="K9" s="18" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>번역=P8b 분리, ⚠ app.py 재시작</t>
         </is>
@@ -2565,23 +5093,23 @@
           <t>번역 캐시 스키마 + 뷰어별 언어 + translator↔chat 연결</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="14">
         <f>IF(F10="✅",1,IF(F10="🔄",0.5,IF(F10="◑",0.7,IF(F10="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H10" s="17" t="inlineStr"/>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr"/>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>키 확보 후</t>
         </is>
       </c>
-      <c r="J10" s="18" t="inlineStr"/>
-      <c r="K10" s="18" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr"/>
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t>Google/DeepL 키 확보 후</t>
         </is>
@@ -2614,23 +5142,23 @@
           <t>Coupons·Stamps mock→실연동</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="14">
         <f>IF(F11="✅",1,IF(F11="🔄",0.5,IF(F11="◑",0.7,IF(F11="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H11" s="17" t="inlineStr"/>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr"/>
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr"/>
-      <c r="K11" s="18" t="inlineStr"/>
+      <c r="J11" s="16" t="inlineStr"/>
+      <c r="K11" s="16" t="inlineStr"/>
       <c r="L11" s="12" t="n"/>
     </row>
     <row r="12">
@@ -2659,23 +5187,23 @@
           <t>Notifications 실연동 + mobile 라우팅</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="14">
         <f>IF(F12="✅",1,IF(F12="🔄",0.5,IF(F12="◑",0.7,IF(F12="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H12" s="17" t="inlineStr"/>
-      <c r="I12" s="18" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr"/>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J12" s="18" t="inlineStr"/>
-      <c r="K12" s="18" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr"/>
+      <c r="K12" s="16" t="inlineStr"/>
       <c r="L12" s="12" t="n"/>
     </row>
     <row r="13">
@@ -2704,23 +5232,23 @@
           <t>Dashboard·StaffManagement 실연동</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="14">
         <f>IF(F13="✅",1,IF(F13="🔄",0.5,IF(F13="◑",0.7,IF(F13="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H13" s="17" t="inlineStr"/>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr"/>
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J13" s="18" t="inlineStr"/>
-      <c r="K13" s="18" t="inlineStr"/>
+      <c r="J13" s="16" t="inlineStr"/>
+      <c r="K13" s="16" t="inlineStr"/>
       <c r="L13" s="12" t="n"/>
     </row>
     <row r="14">
@@ -2749,23 +5277,23 @@
           <t>consent placeholder + dev 정보 제거 + 앱 버전 동적화</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="14">
         <f>IF(F14="✅",1,IF(F14="🔄",0.5,IF(F14="◑",0.7,IF(F14="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H14" s="17" t="inlineStr"/>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr"/>
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr"/>
-      <c r="K14" s="18" t="inlineStr"/>
+      <c r="J14" s="16" t="inlineStr"/>
+      <c r="K14" s="16" t="inlineStr"/>
       <c r="L14" s="12" t="n"/>
     </row>
     <row r="15">
@@ -2794,23 +5322,23 @@
           <t>환불·청소년·쿠키 정책</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="14">
         <f>IF(F15="✅",1,IF(F15="🔄",0.5,IF(F15="◑",0.7,IF(F15="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H15" s="17" t="inlineStr"/>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr"/>
+      <c r="I15" s="16" t="inlineStr">
         <is>
           <t>2026-06-중</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr"/>
-      <c r="K15" s="18" t="inlineStr"/>
+      <c r="J15" s="16" t="inlineStr"/>
+      <c r="K15" s="16" t="inlineStr"/>
       <c r="L15" s="12" t="n"/>
     </row>
     <row r="16">
@@ -2839,23 +5367,23 @@
           <t>wifi_profiles 확장 + beacon_wifi·units·grant·devices</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="14">
         <f>IF(F16="✅",1,IF(F16="🔄",0.5,IF(F16="◑",0.7,IF(F16="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H16" s="17" t="inlineStr"/>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr"/>
+      <c r="I16" s="16" t="inlineStr">
         <is>
           <t>2026-06-말~7월초</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr"/>
-      <c r="K16" s="18" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr"/>
+      <c r="K16" s="16" t="inlineStr"/>
       <c r="L16" s="12" t="n"/>
     </row>
     <row r="17">
@@ -2884,23 +5412,23 @@
           <t>handshake 묶음 + admin WiFi 등록 + provider WifiSettings</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="14">
         <f>IF(F17="✅",1,IF(F17="🔄",0.5,IF(F17="◑",0.7,IF(F17="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H17" s="17" t="inlineStr"/>
-      <c r="I17" s="18" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr"/>
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t>2026-07-초</t>
         </is>
       </c>
-      <c r="J17" s="18" t="inlineStr"/>
-      <c r="K17" s="18" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr"/>
+      <c r="K17" s="16" t="inlineStr"/>
       <c r="L17" s="12" t="n"/>
     </row>
     <row r="18">
@@ -2929,23 +5457,23 @@
           <t>비콘→WiFi 묶음 fetch + BSSID 검증</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="14">
         <f>IF(F18="✅",1,IF(F18="🔄",0.5,IF(F18="◑",0.7,IF(F18="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H18" s="17" t="inlineStr"/>
-      <c r="I18" s="18" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr"/>
+      <c r="I18" s="16" t="inlineStr">
         <is>
           <t>2026-07-초</t>
         </is>
       </c>
-      <c r="J18" s="18" t="inlineStr"/>
-      <c r="K18" s="18" t="inlineStr"/>
+      <c r="J18" s="16" t="inlineStr"/>
+      <c r="K18" s="16" t="inlineStr"/>
       <c r="L18" s="12" t="n"/>
     </row>
     <row r="19">
@@ -2974,23 +5502,23 @@
           <t>.mobileconfig 생성·다건 설치</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="14">
         <f>IF(F19="✅",1,IF(F19="🔄",0.5,IF(F19="◑",0.7,IF(F19="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H19" s="17" t="inlineStr"/>
-      <c r="I19" s="18" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr"/>
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J19" s="18" t="inlineStr"/>
-      <c r="K19" s="18" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr"/>
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>서명은 인증서 후</t>
         </is>
@@ -3023,23 +5551,23 @@
           <t>비번 교체 리마인드 + 인가 손님 자동 전파</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="14">
         <f>IF(F20="✅",1,IF(F20="🔄",0.5,IF(F20="◑",0.7,IF(F20="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H20" s="17" t="inlineStr"/>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr"/>
+      <c r="I20" s="16" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J20" s="18" t="inlineStr"/>
-      <c r="K20" s="18" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr"/>
+      <c r="K20" s="16" t="inlineStr">
         <is>
           <t>v1 flag 비공개</t>
         </is>
@@ -3072,23 +5600,23 @@
           <t>호실·자리 시간제 권한 UI</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="14">
         <f>IF(F21="✅",1,IF(F21="🔄",0.5,IF(F21="◑",0.7,IF(F21="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H21" s="17" t="inlineStr"/>
-      <c r="I21" s="18" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr"/>
+      <c r="I21" s="16" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J21" s="18" t="inlineStr"/>
-      <c r="K21" s="18" t="inlineStr">
+      <c r="J21" s="16" t="inlineStr"/>
+      <c r="K21" s="16" t="inlineStr">
         <is>
           <t>v1 flag 비공개</t>
         </is>
@@ -3121,23 +5649,23 @@
           <t>admin app-versions UI + mobile OS 최소버전 게이트</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="14">
         <f>IF(F22="✅",1,IF(F22="🔄",0.5,IF(F22="◑",0.7,IF(F22="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H22" s="17" t="inlineStr"/>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr"/>
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J22" s="18" t="inlineStr"/>
-      <c r="K22" s="18" t="inlineStr"/>
+      <c r="J22" s="16" t="inlineStr"/>
+      <c r="K22" s="16" t="inlineStr"/>
       <c r="L22" s="12" t="n"/>
     </row>
     <row r="23">
@@ -3166,23 +5694,23 @@
           <t>PrivacyInfo.xcprivacy + Bundle ID + Photo Picker</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="14">
         <f>IF(F23="✅",1,IF(F23="🔄",0.5,IF(F23="◑",0.7,IF(F23="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H23" s="17" t="inlineStr"/>
-      <c r="I23" s="18" t="inlineStr">
+      <c r="H23" s="15" t="inlineStr"/>
+      <c r="I23" s="16" t="inlineStr">
         <is>
           <t>2026-07-중</t>
         </is>
       </c>
-      <c r="J23" s="18" t="inlineStr"/>
-      <c r="K23" s="18" t="inlineStr"/>
+      <c r="J23" s="16" t="inlineStr"/>
+      <c r="K23" s="16" t="inlineStr"/>
       <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
@@ -3211,23 +5739,23 @@
           <t>회원 QR + provider 스캔/코드입력 + 친구초대 QR</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="14">
         <f>IF(F24="✅",1,IF(F24="🔄",0.5,IF(F24="◑",0.7,IF(F24="🔎",0.9,0))))</f>
         <v/>
       </c>
-      <c r="H24" s="17" t="inlineStr"/>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="H24" s="15" t="inlineStr"/>
+      <c r="I24" s="16" t="inlineStr">
         <is>
           <t>2026-07-초~중</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr"/>
-      <c r="K24" s="18" t="inlineStr">
+      <c r="J24" s="16" t="inlineStr"/>
+      <c r="K24" s="16" t="inlineStr">
         <is>
           <t>P9 이후 병행</t>
         </is>

--- a/docs/exports/pathwave_dev_checklist.xlsx
+++ b/docs/exports/pathwave_dev_checklist.xlsx
@@ -578,11 +578,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -663,11 +663,11 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>검토중 (🔎)</t>
+          <t>대기 (⬜)</t>
         </is>
       </c>
       <c r="B8" s="5">
-        <f>COUNTIF('Phase 1 PR 체크리스트'!F2:F30,"🔎")</f>
+        <f>COUNTIF('Phase 1 PR 체크리스트'!F2:F30,"⬜")</f>
         <v/>
       </c>
       <c r="C8" s="2" t="n"/>
@@ -675,11 +675,11 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>대기 (⬜)</t>
-        </is>
-      </c>
-      <c r="B9" s="5">
-        <f>COUNTIF('Phase 1 PR 체크리스트'!F2:F30,"⬜")</f>
+          <t>가중 평균 진척율</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>AVERAGE('Phase 1 PR 체크리스트'!G2:G30)</f>
         <v/>
       </c>
       <c r="C9" s="2" t="n"/>
@@ -687,24 +687,25 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>가중 평균 진척율</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>AVERAGE('Phase 1 PR 체크리스트'!G2:G30)</f>
-        <v/>
+          <t>업데이트 일자</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
       </c>
       <c r="C10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>업데이트 일자</t>
+          <t>외부 서비스 신청 시작</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-02 주</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -712,12 +713,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>외부 서비스 신청 시작</t>
+          <t>Phase 1.5 개발환경+테스트</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-02 주</t>
+          <t>2026-07 중~하순</t>
         </is>
       </c>
       <c r="C12" s="2" t="n"/>
@@ -725,102 +726,89 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Phase 1.5 개발환경+테스트</t>
+          <t>목표 출시일</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-07 중~하순 (신규 단계)</t>
+          <t>2026-07-하순~8월 초</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>목표 출시일</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-하순~8월 초</t>
-        </is>
-      </c>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>주체 컬러 범례</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>주체 컬러 범례</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>mobile 앱 손님</t>
+        </is>
+      </c>
       <c r="C15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>사용자</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>mobile 앱 사용자 (앱 손님)</t>
+          <t>provider-web 점주</t>
         </is>
       </c>
       <c r="C16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>provider-web 점주</t>
+          <t>admin-web 운영자</t>
         </is>
       </c>
       <c r="C17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>admin-web 운영자</t>
+          <t>Pathwave 백엔드 (API/DB/번역/푸시 등 공통)</t>
         </is>
       </c>
       <c r="C18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>인프라</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>백엔드 (다중 영향)</t>
+          <t>서버·운영도구·자동화·심의 메타</t>
         </is>
       </c>
       <c r="C19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>운영 인프라/도구/심의 메타</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -836,14 +824,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
@@ -851,7 +839,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PathWave 기능별 전체 작업 현황 — 주체별 + 이전 완료 / Phase 1 / 남은</t>
+          <t>PathWave 기능별 전체 현황 — 주체별 sub-feature × 이전/Phase 1/남은</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -888,7 +876,7 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>항목</t>
+          <t>sub-feature</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -910,7 +898,7 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
@@ -925,12 +913,12 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>이메일 인증·가입 API</t>
+          <t>이메일 인증</t>
         </is>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>/api/auth send-code·verify-code·register·login + email_codes + bcrypt + JWT</t>
+          <t>/api/auth send-code·verify-code + email_codes 테이블 + 5분 만료</t>
         </is>
       </c>
       <c r="F4" s="17" t="inlineStr">
@@ -943,7 +931,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -958,12 +946,12 @@
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>5종 소셜 로그인 BE</t>
+          <t>이메일 회원가입</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>Google·Apple·Facebook·Kakao·Naver 토큰 검증 + 동의 처리</t>
+          <t>/api/auth/register + bcrypt + 약관 동의 record_consents</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
@@ -971,16 +959,12 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>실 키는 카카오·네이버 검수 후</t>
-        </is>
-      </c>
+      <c r="G5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -995,12 +979,12 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>동의·약관·미성년자 BE</t>
+          <t>이메일 로그인</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>8 KIND 정책 + record_consents 감사 + parent_invite 코드</t>
+          <t>/api/auth/login + JWT 발급(access+refresh)</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
@@ -1013,7 +997,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
@@ -1028,12 +1012,12 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>회원 탈퇴 + 14일 그레이스</t>
+          <t>5종 소셜 로그인 토큰 검증</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>/api/auth/delete-account + soft delete + deleted_at</t>
+          <t>Google·Apple·Facebook·Kakao·Naver token verify + 사용자 매핑</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
@@ -1041,12 +1025,16 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr"/>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>실 키는 카카오·네이버 검수 후</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
@@ -1061,12 +1049,12 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>모바일 비번 재설정 BE</t>
+          <t>동의·약관 8 KIND</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>/api/auth/forgot-password·reset-password (users 테이블)</t>
+          <t>policies(terms/privacy/location/marketing/push/camera/storage/third_party/age14) 등록·버전관리</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
@@ -1079,7 +1067,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
@@ -1094,12 +1082,12 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>시설 계정 가입·로그인 BE</t>
+          <t>미성년자 보호 + 부모 초대</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>/api/facility send-code·register·login + 운영자 승인 대기</t>
+          <t>parent_invite 코드 발급/검증 + age14 동의 흐름</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -1112,7 +1100,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
@@ -1122,359 +1110,347 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>회원 탈퇴 + 14일 그레이스</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>/api/auth/delete-account + soft delete + deleted_at + 재가입 차단</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>모바일 비번 재설정 API</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>/api/auth/forgot-password·reset-password (users 테이블)</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>시설 계정 가입·로그인</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>/api/facility send-code·register·login + facility_accounts + 운영자 승인 대기</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
           <t>Phase 1 ✅</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>P4 — 시설 비번 재설정 BE 신규</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>/api/facility/forgot-password·reset-password 신규 (email_codes 재활용)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>P4 — 시설 비번 재설정 API 신규</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>/api/facility/forgot-password·reset-password 신규(email_codes 재활용)</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>인증/회원가입</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>mobile 가입 5단계</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>consent → 본인인증 → 이메일/소셜 → 약관 동의 → 완료</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>mobile 가입 5단계 흐름</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>consent → 본인인증 → 이메일/소셜 → 약관 → 완료</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>인증/회원가입</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>mobile 로그인·비번재설정</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>login_screen + forgot_password_screen (2단계 코드)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>mobile login_screen</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>이메일 로그인 + 5종 소셜 버튼 + forgot password 링크</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B16" s="16" t="inlineStr">
         <is>
           <t>인증/회원가입</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>mobile 회원 탈퇴</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>delete_account_screen + 14일 그레이스</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>mobile forgot_password_screen</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>2단계 — 이메일 입력 → 코드+새비번</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>mobile delete_account_screen</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>탈퇴 안내·확인 + 14일 그레이스 안내</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>시설관리자</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>인증/회원가입</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>provider 회원가입·로그인 UI</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>실 폼 + 소셜로그인 + 매장 정보 입력</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>폼은 dev 우회로 가려졌었음</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>provider 회원가입 폼</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>실 폼 + 매장 정보 + 소셜 로그인</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>시설관리자</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>인증/회원가입</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>provider Login.jsx</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>실 폼 존재했으나 dev 우회로 가려졌었음</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>Phase 1 ✅</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>P4 — provider dev 우회 제거</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>DEV_AUTO_LOGIN env 게이트 + Login 자동토큰 제거 + Signup 게스트 게이트</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>출시 빌드에서 실 로그인폼 노출</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>인증/회원가입</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 ✅</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>P4 — provider ForgotPassword 페이지</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>/forgot-password 라우트 + 2단계 UI + AuthService 메서드</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>인증/회원가입</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>admin Login + 관리자 인증</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>admin-web Login + JWT + RequireAuth</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>인증/회원가입</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>남은</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>실 키 검증</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>카카오·네이버 검수 완료 후 실 소셜로그인 통합 테스트</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>외부 활성화 후</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>매장 정보</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>매장 CRUD API</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>/api/facilities CRUD + 이미지 갤러리 + 다국어 번역 캐시</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>매장 정보</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>mobile 매장 상세 화면</t>
+          <t>P4 — dev 우회 env 게이트</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>facility_screen — 이미지/영업시간/주소/채팅 진입</t>
+          <t>DEV_AUTO_LOGIN = import.meta.env.DEV (출시빌드 비활성)</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -1492,22 +1468,22 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>매장 정보</t>
+          <t>인증/회원가입</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>provider StoreInfo UI 골격</t>
+          <t>P4 — Login 자동토큰 제거</t>
         </is>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>편집/저장/지도/이미지/비콘 claim UI 완성, 데이터는 mock</t>
+          <t>useEffect 자동 mock 토큰 발급 제거 → 실 로그인 폼 노출</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -1515,11 +1491,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>데이터 연동은 P5</t>
-        </is>
-      </c>
+      <c r="G21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
@@ -1529,7 +1501,7 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>매장 정보</t>
+          <t>인증/회원가입</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -1539,12 +1511,12 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>P5 — provider StoreInfo 실연동</t>
+          <t>P4 — Signup 게스트 게이트</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>StoreService.list/update PATCH 실연동 + 실 fid 비콘 claim</t>
+          <t>"로그인 없이 이용" 버튼 dev 환경에서만 노출</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -1562,75 +1534,75 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>P4 — ForgotPassword 신규</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>provider /forgot-password 라우트 + 2단계 UI + AuthService 메서드 추가</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>인증/회원가입</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>admin Login</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>admin-web Login + RequireAuth (DevPreviewBar는 VITE_PREVIEW_MODE 게이트됨)</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
           <t>매장 정보</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 ✅</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>P5 — Settings 푸터 PwFooter</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>CompanyInfoService → 실 법인정보</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>매장 정보</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 ✅</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>P5 — dead code 정리</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>Facilities.jsx (1계정1매장 위반) 삭제</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>매장 정보</t>
-        </is>
-      </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
           <t>이전 완료</t>
@@ -1638,12 +1610,12 @@
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>admin Stores 관리</t>
+          <t>매장 CRUD API</t>
         </is>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>매장 관리 + 비콘 매핑 + 번역 등록</t>
+          <t>/api/facilities POST/GET/PATCH/DELETE + owner 권한</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
@@ -1656,7 +1628,7 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
@@ -1666,39 +1638,35 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>남은</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>P8c — 스키마 갭</t>
+          <t>매장 이미지 갤러리</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>facilities 테이블 category/holidays/detailAddress 추가 또는 UI 정리</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>별도 작업 칩</t>
-        </is>
-      </c>
+          <t>/api/facilities/&lt;id&gt;/images CRUD</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>결제·구독</t>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
@@ -1708,12 +1676,12 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>billing API 전체</t>
+          <t>다국어 번역 캐시</t>
         </is>
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>/api/billing cards·subscriptions·payments·refund·extend·receipt-email + PG 추상화</t>
+          <t>facilities/translations join — 12언어</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
@@ -1724,14 +1692,14 @@
       <c r="G27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>결제·구독</t>
+          <t>매장 정보</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
@@ -1741,12 +1709,12 @@
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>provider PaymentManagement·Subscriptions UI 골격</t>
+          <t>비콘 claim·list API</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>다단계 결제 흐름/카드 입력/구독 카드 UI, 데이터는 mock + localStorage 평문저장</t>
+          <t>/api/store/&lt;id&gt;/beacons + /claim-beacon (Phase C)</t>
         </is>
       </c>
       <c r="F28" s="17" t="inlineStr">
@@ -1757,29 +1725,29 @@
       <c r="G28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>결제·구독</t>
+          <t>매장 정보</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 ✅</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>P7 — BillingService 신규</t>
+          <t>company_info API (Phase M)</t>
         </is>
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>provider /api/billing 래퍼 7종 메서드</t>
+          <t>슈퍼어드민 입력 GET /api/company-info</t>
         </is>
       </c>
       <c r="F29" s="17" t="inlineStr">
@@ -1790,29 +1758,29 @@
       <c r="G29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>결제·구독</t>
+          <t>매장 정보</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 ✅</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>P7 — 카드 평문저장 제거 (C6)</t>
+          <t>mobile facility_screen</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>localStorage pathwave_payment_card + audit 큐 완전 제거, brand+last4만 전송</t>
+          <t>이미지/영업시간/주소/카테고리/채팅 진입 + 즐겨찾기</t>
         </is>
       </c>
       <c r="F30" s="17" t="inlineStr">
@@ -1820,11 +1788,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>PCI 준수</t>
-        </is>
-      </c>
+      <c r="G30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
@@ -1834,351 +1798,343 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>provider StoreInfo UI 골격</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>편집/저장/지도(leaflet)/이미지/카테고리/영업시간/휴무/비콘 claim — 데이터는 mock</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>P5 — StoreInfo 마운트 로드</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>StoreService.list() → 1계정1매장 → setStore + fid</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>P5 — handleSave PATCH 연동</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>StoreService.update(fid, payload) — business_hours 양방향 매핑</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>P5 — 비콘 fid 실연동</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>MOCK_FID="demo" 제거 → 실 fid로 fetchBeacons·claimBeacon</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>P5 — Settings 푸터 PwFooter</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>하드코딩 시원컴퍼니/서초구 → CompanyInfoService 실 법인정보</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>P5 — Facilities dead code 삭제</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>1계정1매장 위반 + 라우트 미연결 파일 + import 제거</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>admin Stores 관리</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>매장 관리 + 비콘 매핑 + 번역 등록</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>매장 정보</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>P8c — 스키마 갭</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>facilities 테이블 category/holidays/detailAddress 컬럼 추가 또는 UI 정리</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>별도 작업 칩</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
           <t>결제·구독</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 ✅</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>P7 — 결제 흐름 통합</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>PaymentManagement·Subscriptions·ServiceRequest 동일 백엔드로 통합 + 호텔H 기본값 제거</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>카드 등록·삭제·목록 API</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>/api/billing/cards POST/GET/DELETE — last4·PG key 토큰화</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>결제·구독</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>admin Payments + Subscriptions + 환불</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>adminApi.listPayments/listSubscriptions/refundPayment 실연동 + 환불 모달</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>이미 정합</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>구독 생성·해지·연장 API</t>
+        </is>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>/api/billing/subscriptions + cancel + extend</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>결제·구독</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>남은</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>토스 키 활성화</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>토스페이먼츠 심사 통과 후 PG_PROVIDER=toss + 실 결제 검증</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>외부 1~2주</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>쿠폰</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰 발행/사용/만료 API</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>/api/coupons issue·use·expire + 정책 + 통계</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>mobile 쿠폰함</t>
-        </is>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>coupons_screen (active/used/expired 탭) + 사용 다이얼로그</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G35" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰 사용 silent error 잔존</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰</t>
-        </is>
-      </c>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="inlineStr">
-        <is>
-          <t>P9 — mobile silent error 수정</t>
-        </is>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>사용 실패 시 사용자 피드백 + 목록 갱신</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G36" s="16" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="inlineStr">
-        <is>
-          <t>P22 — 회원 QR (사용자 측)</t>
-        </is>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>mobile 마이페이지 회원 QR (URL 토큰)</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G37" s="16" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
-        <is>
-          <t>provider Coupons·CouponForm UI</t>
-        </is>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰 목록·생성·통계 UI 완성, 데이터는 mock</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G38" s="16" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>P9 — provider Coupons 실연동</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>mock → /api/coupons 실연동, 발행/회수 정상 흐름</t>
-        </is>
-      </c>
-      <c r="F39" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G39" s="16" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰</t>
-        </is>
-      </c>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="inlineStr">
-        <is>
-          <t>P22 — provider 스캔/적립</t>
-        </is>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>회원 QR 스캔/코드입력 → 적립·사용</t>
-        </is>
-      </c>
-      <c r="F40" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G40" s="16" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>쿠폰</t>
-        </is>
-      </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
           <t>이전 완료</t>
@@ -2186,12 +2142,12 @@
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>admin 쿠폰 통계</t>
+          <t>결제 내역·환불 API</t>
         </is>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>admin coupon stats API + UI</t>
+          <t>/api/billing/payments + admin refund</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -2199,21 +2155,17 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
-        <is>
-          <t>CouponStats placeholder 일부 → P11</t>
-        </is>
-      </c>
+      <c r="G41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>스탬프</t>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
@@ -2223,12 +2175,12 @@
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>스탬프 적립/리워드 API</t>
+          <t>영수증 이메일 + PG 추상화</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>/api/stamps accrue/list + 시설별 정책 + BLE 자동 적립</t>
+          <t>/api/billing/receipt-email + PG provider(sim/toss)</t>
         </is>
       </c>
       <c r="F42" s="17" t="inlineStr">
@@ -2236,17 +2188,21 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G42" s="16" t="inlineStr"/>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>키 활성화 시 toss 전환</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
         </is>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>스탬프</t>
+          <t>결제·구독</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
@@ -2256,12 +2212,12 @@
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>mobile 스탬프 화면</t>
+          <t>provider PaymentManagement UI 골격</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>stamps_screen — 시설별 카드/진행률/보상</t>
+          <t>다단계 결제 흐름/카드 입력 모달/내역/구독 카드 — 데이터는 mock + localStorage 평문저장</t>
         </is>
       </c>
       <c r="F43" s="17" t="inlineStr">
@@ -2279,22 +2235,22 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>스탬프</t>
+          <t>결제·구독</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>provider Stamps·StampForm UI</t>
+          <t>P7 — BillingService 신규</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>정책·통계 UI 완성, 데이터는 mock</t>
+          <t>7종 메서드 래퍼 (cards/subs/payments/receipt-email) + PCI 주석</t>
         </is>
       </c>
       <c r="F44" s="17" t="inlineStr">
@@ -2312,30 +2268,34 @@
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>스탬프</t>
+          <t>결제·구독</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>P9 — provider Stamps 실연동</t>
+          <t>P7 — 카드 localStorage 평문저장 제거 (C6)</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>mock → /api/stamps 실연동</t>
-        </is>
-      </c>
-      <c r="F45" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="inlineStr"/>
+          <t>pathwave_payment_card + audit 큐 완전 제거 → brand+last4 만 전송</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>PCI 준수</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
@@ -2345,40 +2305,40 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>스탬프</t>
+          <t>결제·구독</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>P22 — 수동 적립(staff)</t>
+          <t>P7 — 결제 흐름 통합</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>회원 QR 스캔 → 스탬프 수동 적립 (auto/staff 모드)</t>
-        </is>
-      </c>
-      <c r="F46" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>PaymentManagement·Subscriptions·ServiceRequest 동일 백엔드 통합</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="inlineStr">
-        <is>
-          <t>채팅</t>
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>결제·구독</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
@@ -2388,12 +2348,12 @@
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>chat 전체 API</t>
+          <t>admin Payments + Subscriptions + 환불</t>
         </is>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
-          <t>/api/chat rooms·messages·SSE 스트림·read + chat_blocks + is_blocked 가드</t>
+          <t>adminApi.listPayments/listSubscriptions/refundPayment 실연동 + 환불 모달</t>
         </is>
       </c>
       <c r="F47" s="17" t="inlineStr">
@@ -2406,60 +2366,64 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>결제·구독</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>남은</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>abuse_reports + chat_blocks</t>
+          <t>토스 키 활성화 + 실결제</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>/api/abuse-reports + /api/admin/abuse-reports + /api/blocks</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="inlineStr"/>
+          <t>심사 통과 후 PG_PROVIDER=toss + 실 결제 end-to-end</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>외부 1~2주</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>채팅</t>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 ✅</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>P8 — /api/chat/reports 신규</t>
+          <t>쿠폰 발행/사용/만료 API</t>
         </is>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>abuse_reports → ChatMonitor용 신고 큐 변환, super_admin 가드</t>
+          <t>/api/coupons issue·use·expire + 정책 + 통계</t>
         </is>
       </c>
       <c r="F49" s="17" t="inlineStr">
@@ -2467,11 +2431,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
-        <is>
-          <t>⚠ app.py 재시작 후 활성</t>
-        </is>
-      </c>
+      <c r="G49" s="16" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
@@ -2481,7 +2441,7 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -2491,12 +2451,12 @@
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>mobile 채팅 화면</t>
+          <t>mobile coupons_screen</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>chat_list_screen + chat_detail_screen (SSE 실시간) + 신고/차단 + 가이드라인 모달</t>
+          <t>활성/사용/만료 탭 + 사용 다이얼로그</t>
         </is>
       </c>
       <c r="F50" s="17" t="inlineStr">
@@ -2506,7 +2466,7 @@
       </c>
       <c r="G50" s="16" t="inlineStr">
         <is>
-          <t>재연결 미지원이었음</t>
+          <t>사용 silent error 잔존</t>
         </is>
       </c>
     </row>
@@ -2518,27 +2478,27 @@
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 ✅</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>P8 — mobile SSE 재연결</t>
+          <t>P9 — mobile silent error 수정</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>StreamController 기반, 지수 backoff(1→30s), ?after_id= 누락 보충</t>
-        </is>
-      </c>
-      <c r="F51" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>사용 실패 시 사용자 피드백 + 목록 갱신</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="G51" s="16" t="inlineStr"/>
@@ -2551,22 +2511,22 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>남은 — P8b</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>뷰어별 번역 표시</t>
+          <t>P22 — 회원 QR 발급(URL 토큰)</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>list_messages·SSE 응답에 ?lang= 기준 번역 포함 → mobile UI 노출</t>
+          <t>마이페이지 회원 QR + 토큰 만료/재발급</t>
         </is>
       </c>
       <c r="F52" s="21" t="inlineStr">
@@ -2574,11 +2534,7 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>USP 기능</t>
-        </is>
-      </c>
+      <c r="G52" s="16" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
@@ -2588,7 +2544,7 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
@@ -2598,12 +2554,12 @@
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>provider CustomerChat UI 골격</t>
+          <t>provider Coupons UI 골격</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>대화창 UI 완성, 데이터는 DUMMY_CHATS 7개 더미</t>
+          <t>쿠폰 목록 UI 완성, 데이터 mock</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr">
@@ -2621,7 +2577,7 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
@@ -2631,12 +2587,12 @@
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>provider ChatService 메서드</t>
+          <t>provider CouponForm UI 골격</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>openRoom/listRooms/listMessages/sendMessage/markRead/subscribe(SSE) 다 작성됨</t>
+          <t>쿠폰 생성·통계 UI</t>
         </is>
       </c>
       <c r="F54" s="17" t="inlineStr">
@@ -2644,11 +2600,7 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>호출만 안 되고 있었음</t>
-        </is>
-      </c>
+      <c r="G54" s="16" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
@@ -2658,27 +2610,27 @@
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 ✅</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>P8 — provider CustomerChat 실연동</t>
+          <t>P9 — provider Coupons 실연동</t>
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
-          <t>DUMMY 제거 → ChatService 5종 호출 + 30초 폴링 + 낙관적 전송 + SSE 정리</t>
-        </is>
-      </c>
-      <c r="F55" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>mock → /api/coupons 실연동</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr"/>
@@ -2691,22 +2643,22 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>남은 — P8b</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>provider 번역 표시</t>
+          <t>P22 — provider QR 스캔/적립·사용</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>CustomerChat translation 필드 실데이터 노출</t>
+          <t>회원 QR 스캔 + 코드 입력 → 적립/사용</t>
         </is>
       </c>
       <c r="F56" s="21" t="inlineStr">
@@ -2724,7 +2676,7 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
@@ -2734,12 +2686,12 @@
       </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
-          <t>admin abuse + chat_blocks 처리</t>
+          <t>admin 쿠폰 통계 API</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>admin abuse_reports CRUD + chat_blocks 관리</t>
+          <t>admin coupon stats</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr">
@@ -2749,7 +2701,7 @@
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>PR #142</t>
+          <t>CouponStats placeholder → P11</t>
         </is>
       </c>
     </row>
@@ -2761,27 +2713,27 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>쿠폰</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>admin ChatMonitor UI</t>
+          <t>P11 — CouponStats 실연동</t>
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>신고 큐 테이블 UI 완성, /api/chat/reports 엔드포인트만 없었음</t>
-        </is>
-      </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>admin placeholder 해소</t>
+        </is>
+      </c>
+      <c r="F58" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr"/>
@@ -2789,49 +2741,45 @@
     <row r="59">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>채팅</t>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>스탬프</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>남은 — P8b</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
         <is>
-          <t>번역 캐시 스키마</t>
+          <t>스탬프 적립 API + 정책</t>
         </is>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
-          <t>chat_message_translations 캐시 테이블 + translator.py 연결</t>
-        </is>
-      </c>
-      <c r="F59" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G59" s="16" t="inlineStr">
-        <is>
-          <t>DeepL/Google Translate 키 후</t>
-        </is>
-      </c>
+          <t>/api/stamps accrue/list + 시설별 정책</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>알림</t>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>스탬프</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
@@ -2841,12 +2789,12 @@
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>알림 API + 카테고리</t>
+          <t>비콘 자동 적립</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>/api/notifications inbox·announcements·read + notification_preferences</t>
+          <t>BLE 비콘 감지 → 자동 적립</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
@@ -2857,14 +2805,14 @@
       <c r="G60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>스탬프</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
@@ -2874,12 +2822,12 @@
       </c>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>iOS APNs 직접 (PR #50)</t>
+          <t>mobile stamps_screen</t>
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
-          <t>APNs HTTP/2 + JWT ES256 — Apple 인증서/키만 필요</t>
+          <t>시설별 카드/진행률/보상 표시</t>
         </is>
       </c>
       <c r="F61" s="17" t="inlineStr">
@@ -2887,21 +2835,17 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G61" s="16" t="inlineStr">
-        <is>
-          <t>자체구축 — Firebase 미사용</t>
-        </is>
-      </c>
+      <c r="G61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>스탬프</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
@@ -2911,12 +2855,12 @@
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>Android 푸시</t>
+          <t>provider Stamps UI 골격</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>FCM 통합 (PR #44) — Google Play Services 의존</t>
+          <t>정책·통계 UI</t>
         </is>
       </c>
       <c r="F62" s="17" t="inlineStr">
@@ -2924,21 +2868,17 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
-        <is>
-          <t>⚠ 현실적으로 Android 자체구축 불가, FCM 무료 무제한이라 그대로 사용 권장</t>
-        </is>
-      </c>
+      <c r="G62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
+      <c r="A63" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>스탬프</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
@@ -2948,12 +2888,12 @@
       </c>
       <c r="D63" s="16" t="inlineStr">
         <is>
-          <t>mobile 알림 화면 + 권한 동의</t>
+          <t>provider StampForm UI 골격</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>notifications_screen (인박스/공지 탭) + notification_permission_dialog</t>
+          <t>스탬프 정책 폼</t>
         </is>
       </c>
       <c r="F63" s="17" t="inlineStr">
@@ -2961,21 +2901,17 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G63" s="16" t="inlineStr">
-        <is>
-          <t>라우팅 보강 필요</t>
-        </is>
-      </c>
+      <c r="G63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>스탬프</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
@@ -2985,12 +2921,12 @@
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>P10 — mobile 알림 라우팅</t>
+          <t>P9 — provider Stamps 실연동</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>알림 종류별 화면 이동 (coupon→쿠폰함, chat→채팅)</t>
+          <t>mock → /api/stamps 실연동</t>
         </is>
       </c>
       <c r="F64" s="21" t="inlineStr">
@@ -3008,73 +2944,73 @@
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>스탬프</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
         <is>
-          <t>provider Notifications UI</t>
+          <t>P22 — 수동 적립(staff)</t>
         </is>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
-          <t>받은 알림 + 시스템 공지 UI 완성, 데이터는 mockInbox 14건</t>
-        </is>
-      </c>
-      <c r="F65" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>회원 QR 스캔 → 수동 적립 (auto/staff 모드)</t>
+        </is>
+      </c>
+      <c r="F65" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>알림</t>
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>P10 — provider Notifications 실연동</t>
+          <t>채팅방·메시지 API</t>
         </is>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
-          <t>mockInbox 제거 → /api/notifications 실연동</t>
-        </is>
-      </c>
-      <c r="F66" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>/api/chat rooms·messages + 페이지네이션</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="G66" s="16" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
@@ -3084,12 +3020,12 @@
       </c>
       <c r="D67" s="16" t="inlineStr">
         <is>
-          <t>admin 공지 CRUD + 발송</t>
+          <t>SSE 실시간 스트림</t>
         </is>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
-          <t>admin Announcements CRUD + 실 푸시 발송 통합</t>
+          <t>GET /api/chat/rooms/&lt;id&gt;/stream + 5분 의도 종료 + after_id 지원</t>
         </is>
       </c>
       <c r="F67" s="17" t="inlineStr">
@@ -3102,12 +3038,12 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>WiFi (1회 연결)</t>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
@@ -3117,12 +3053,12 @@
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>wifi_profiles + handshake</t>
+          <t>읽음 처리 + chat_blocks</t>
         </is>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
-          <t>/api/beacon/wifi handshake (LIMIT 1) + wifi_profiles 기본</t>
+          <t>POST /read + is_blocked 가드</t>
         </is>
       </c>
       <c r="F68" s="17" t="inlineStr">
@@ -3130,217 +3066,205 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G68" s="16" t="inlineStr">
-        <is>
-          <t>로밍은 LIMIT 1 → 묶음 반환으로 확장 필요</t>
-        </is>
-      </c>
+      <c r="G68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>abuse_reports</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>/api/abuse-reports + /api/admin/abuse-reports CRUD + PATCH</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G69" s="16" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>P8 — /api/chat/reports 신규</t>
+        </is>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>abuse_reports → ChatMonitor 형태 변환, super_admin 가드</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B69" s="16" t="inlineStr">
-        <is>
-          <t>WiFi (1회 연결)</t>
-        </is>
-      </c>
-      <c r="C69" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="inlineStr">
-        <is>
-          <t>mobile native plugin</t>
-        </is>
-      </c>
-      <c r="E69" s="16" t="inlineStr">
-        <is>
-          <t>iOS NEHotspotConfiguration + Android WifiNetworkSuggestion (자동 가입)</t>
-        </is>
-      </c>
-      <c r="F69" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G69" s="16" t="inlineStr">
-        <is>
-          <t>1회 연결만</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>mobile chat_list_screen</t>
+        </is>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>내 채팅방 목록 + 미읽음 배지</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t>WiFi (1회 연결)</t>
-        </is>
-      </c>
-      <c r="C70" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
-        <is>
-          <t>mobile WifiConnectScreen</t>
-        </is>
-      </c>
-      <c r="E70" s="16" t="inlineStr">
-        <is>
-          <t>BLE 핸드셰이크 → WiFi 정보 전달 + OS 자동 가입 트리거</t>
-        </is>
-      </c>
-      <c r="F70" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G70" s="16" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
-        <is>
-          <t>WiFi (1회 연결)</t>
-        </is>
-      </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D71" s="16" t="inlineStr">
-        <is>
-          <t>provider WifiSettings UI</t>
-        </is>
-      </c>
-      <c r="E71" s="16" t="inlineStr">
-        <is>
-          <t>WiFi 등록·수정·비활성 UI 완성, 가짜 OCR 자동입력 있었음</t>
-        </is>
-      </c>
-      <c r="F71" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G71" s="16" t="inlineStr">
-        <is>
-          <t>OCR 제거됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>WiFi (1회 연결)</t>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>mobile chat_detail_screen</t>
+        </is>
+      </c>
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>SSE 실시간 + 신고/차단 메뉴 + 가이드라인 모달</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G72" s="16" t="inlineStr">
+        <is>
+          <t>재연결 미지원이었음</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
           <t>Phase 1 ✅</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
-        <is>
-          <t>P6 — OCR 허위 제거</t>
-        </is>
-      </c>
-      <c r="E72" s="16" t="inlineStr">
-        <is>
-          <t>runOcrMock 삭제 → 정직한 수동입력 UI, 사진은 참고 첨부로 재정의</t>
-        </is>
-      </c>
-      <c r="F72" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G72" s="16" t="inlineStr">
-        <is>
-          <t>C5 해소</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="inlineStr">
-        <is>
-          <t>WiFi 로밍</t>
-        </is>
-      </c>
-      <c r="C73" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
       <c r="D73" s="16" t="inlineStr">
         <is>
-          <t>P14 — 데이터 모델 재설계</t>
+          <t>P8 — mobile SSE 재연결</t>
         </is>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
-          <t>wifi_profiles 확장 + beacon_wifi·units·wifi_access_grant·devices + beacons.role</t>
-        </is>
-      </c>
-      <c r="F73" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>StreamController + 지수 backoff(1→30s) + ?after_id= 누락 보충</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="G73" s="16" t="inlineStr">
         <is>
-          <t>6/말~7/초</t>
+          <t>⚠ app.py 재시작 후 활성</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>WiFi 로밍</t>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>남은 — P8b</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>P15 — handshake 묶음 + BE</t>
+          <t>mobile 번역 표시 UI</t>
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
-          <t>handshake LIMIT 1 제거 → 묶음 반환</t>
+          <t>translation 필드 실데이터 렌더</t>
         </is>
       </c>
       <c r="F74" s="21" t="inlineStr">
@@ -3358,168 +3282,164 @@
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>WiFi 로밍</t>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
         <is>
-          <t>P15 — provider WifiSettings 실연동 + 비콘 role</t>
+          <t>provider ChatService 메서드</t>
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr">
         <is>
-          <t>비콘 role(wifi/cashier) UI + WiFi 실연동</t>
-        </is>
-      </c>
-      <c r="F75" s="21" t="inlineStr">
+          <t>openRoom/listRooms/listMessages/sendMessage/markRead/subscribe(SSE) — 작성됨, 호출 안 됨</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>provider CustomerChat UI 골격</t>
+        </is>
+      </c>
+      <c r="E76" s="16" t="inlineStr">
+        <is>
+          <t>대화창 UI 완성, DUMMY_CHATS 7개 더미</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B77" s="16" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D77" s="16" t="inlineStr">
+        <is>
+          <t>P8 — CustomerChat 실연동</t>
+        </is>
+      </c>
+      <c r="E77" s="16" t="inlineStr">
+        <is>
+          <t>DUMMY 제거 + ChatService 5종 호출 + 30초 폴링 + 낙관적 전송 + SSE 정리</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G77" s="16" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>남은 — P8b</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>provider 번역 표시</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>translation 필드 실데이터 노출</t>
+        </is>
+      </c>
+      <c r="F78" s="21" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G75" s="16" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="20" t="inlineStr">
+      <c r="G78" s="16" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="20" t="inlineStr">
         <is>
           <t>슈퍼어드민</t>
         </is>
       </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>WiFi 로밍</t>
-        </is>
-      </c>
-      <c r="C76" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D76" s="16" t="inlineStr">
-        <is>
-          <t>P15 — admin WiFi 등록화면</t>
-        </is>
-      </c>
-      <c r="E76" s="16" t="inlineStr">
-        <is>
-          <t>슈퍼어드민용 WiFi 등록 신규 화면</t>
-        </is>
-      </c>
-      <c r="F76" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G76" s="16" t="inlineStr">
-        <is>
-          <t>C10 해소</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B77" s="16" t="inlineStr">
-        <is>
-          <t>WiFi 로밍</t>
-        </is>
-      </c>
-      <c r="C77" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D77" s="16" t="inlineStr">
-        <is>
-          <t>P16 — mobile WiFi 클라이언트</t>
-        </is>
-      </c>
-      <c r="E77" s="16" t="inlineStr">
-        <is>
-          <t>비콘→WiFi 묶음 fetch·캐시 + BSSID 검증 + "WiFi 변경됨" + 손님 자동/승인 + home 진입점</t>
-        </is>
-      </c>
-      <c r="F77" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G77" s="16" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B78" s="16" t="inlineStr">
-        <is>
-          <t>WiFi 로밍</t>
-        </is>
-      </c>
-      <c r="C78" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D78" s="16" t="inlineStr">
-        <is>
-          <t>P17 — .mobileconfig 다건</t>
-        </is>
-      </c>
-      <c r="E78" s="16" t="inlineStr">
-        <is>
-          <t>.mobileconfig 생성·다건 설치 (서명은 Apple 인증서 후)</t>
-        </is>
-      </c>
-      <c r="F78" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G78" s="16" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>WiFi 로밍</t>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
         <is>
-          <t>P18 — credential_mode managed</t>
+          <t>admin abuse·chat_blocks 처리</t>
         </is>
       </c>
       <c r="E79" s="16" t="inlineStr">
         <is>
-          <t>비번 교체 리마인드 + 인가 손님 자동 전파 + 알림 연동</t>
-        </is>
-      </c>
-      <c r="F79" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>abuse PATCH 상태 변경 + chat_blocks 관리</t>
+        </is>
+      </c>
+      <c r="F79" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="G79" s="16" t="inlineStr">
         <is>
-          <t>v1 flag 비공개</t>
+          <t>PR #142</t>
         </is>
       </c>
     </row>
@@ -3531,110 +3451,110 @@
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>WiFi 로밍</t>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>P19 — units/grant 관리</t>
+          <t>admin ChatMonitor UI 골격</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr">
         <is>
-          <t>호실·자리 시간제 권한 관리 UI</t>
-        </is>
-      </c>
-      <c r="F80" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G80" s="16" t="inlineStr">
-        <is>
-          <t>v1 flag 비공개</t>
-        </is>
-      </c>
+          <t>신고 큐 테이블 UI 완성 (엔드포인트만 없었음)</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B81" s="15" t="inlineStr">
-        <is>
-          <t>비콘</t>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>남은 — P8b</t>
         </is>
       </c>
       <c r="D81" s="16" t="inlineStr">
         <is>
-          <t>beacons lifecycle API</t>
+          <t>번역 캐시 스키마 신규</t>
         </is>
       </c>
       <c r="E81" s="16" t="inlineStr">
         <is>
-          <t>beacons 테이블 inventory→active→inactive/lost + claim API</t>
-        </is>
-      </c>
-      <c r="F81" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>chat_message_translations (message_id, lang → translated)</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="G81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>비콘</t>
+          <t>채팅</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>남은 — P8b</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>admin Beacons 인벤토리</t>
+          <t>list_messages·SSE 번역 머지</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr">
         <is>
-          <t>인벤토리 CSV 입고 + claim 모니터 + 배터리·펌웨어 표시</t>
-        </is>
-      </c>
-      <c r="F82" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G82" s="16" t="inlineStr"/>
+          <t>?lang=xx 응답에 translated_text 포함 + translator.py 호출</t>
+        </is>
+      </c>
+      <c r="F82" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>키 활성화 후</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B83" s="16" t="inlineStr">
-        <is>
-          <t>비콘</t>
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>알림</t>
         </is>
       </c>
       <c r="C83" s="16" t="inlineStr">
@@ -3644,12 +3564,12 @@
       </c>
       <c r="D83" s="16" t="inlineStr">
         <is>
-          <t>provider 비콘 claim 흐름</t>
+          <t>알림 inbox·공지 API</t>
         </is>
       </c>
       <c r="E83" s="16" t="inlineStr">
         <is>
-          <t>StoreInfo 내 비콘 claim UI + listBeacons</t>
+          <t>/api/notifications inbox·announcements·read</t>
         </is>
       </c>
       <c r="F83" s="17" t="inlineStr">
@@ -3657,41 +3577,37 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G83" s="16" t="inlineStr">
-        <is>
-          <t>실 fid는 P5 해소</t>
-        </is>
-      </c>
+      <c r="G83" s="16" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>비콘</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>P15 (병합) — beacons.role</t>
+          <t>알림 선호 카테고리</t>
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr">
         <is>
-          <t>beacons.role(wifi/cashier) 컬럼 + admin·provider UI</t>
-        </is>
-      </c>
-      <c r="F84" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>notification_preferences API</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="G84" s="16" t="inlineStr"/>
@@ -3699,12 +3615,12 @@
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>i18n</t>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>알림</t>
         </is>
       </c>
       <c r="C85" s="16" t="inlineStr">
@@ -3714,12 +3630,12 @@
       </c>
       <c r="D85" s="16" t="inlineStr">
         <is>
-          <t>translations API + DeepL 통합</t>
+          <t>iOS APNs 자체 (PR #50)</t>
         </is>
       </c>
       <c r="E85" s="16" t="inlineStr">
         <is>
-          <t>translations 테이블 + GET /api/i18n/{lang} + DeepL 모듈</t>
+          <t>APNs HTTP/2 + JWT ES256 — 자체구축, 인증서/키만 필요</t>
         </is>
       </c>
       <c r="F85" s="17" t="inlineStr">
@@ -3730,14 +3646,14 @@
       <c r="G85" s="16" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>i18n</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C86" s="16" t="inlineStr">
@@ -3747,12 +3663,12 @@
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>admin i18n CRUD</t>
+          <t>Android FCM</t>
         </is>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
-          <t>키별 다국어 입력·수정·자동번역 트리거</t>
+          <t>PR #44 — Google Play Services 의존 (무료 무제한)</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
@@ -3760,42 +3676,46 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G86" s="16" t="inlineStr"/>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>⚠ Android는 FCM 외 사실상 대안 없음</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
         </is>
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>i18n</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C87" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>남은 (자체구축)</t>
         </is>
       </c>
       <c r="D87" s="16" t="inlineStr">
         <is>
-          <t>mobile supportedLocales 7개</t>
+          <t>웹 푸시(VAPID)</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
-          <t>7개 언어 기본, 일부 화면만 적용</t>
-        </is>
-      </c>
-      <c r="F87" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>시설관리자 웹 푸시 자체구축 — Service Worker + Web Push API</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="G87" s="16" t="inlineStr">
         <is>
-          <t>12개로 확장 + 전 화면 → P2</t>
+          <t>시설관리자 알림용</t>
         </is>
       </c>
     </row>
@@ -3807,22 +3727,22 @@
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>i18n</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 ✅</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>P2 — mobile I18nService 통일</t>
+          <t>mobile notifications_screen</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
-          <t>12 supportedLocales + 전 화면 t() 전환 + ko 시드 203→550</t>
+          <t>인박스/공지 탭</t>
         </is>
       </c>
       <c r="F88" s="17" t="inlineStr">
@@ -3830,32 +3750,36 @@
           <t>✅</t>
         </is>
       </c>
-      <c r="G88" s="16" t="inlineStr"/>
+      <c r="G88" s="16" t="inlineStr">
+        <is>
+          <t>라우팅 보강 필요</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
         </is>
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>i18n</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C89" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 ✅</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D89" s="16" t="inlineStr">
         <is>
-          <t>P2 — DeepL 일괄번역 스크립트</t>
+          <t>mobile 권한 동의 다이얼로그</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
-          <t>translate_i18n_deepl.py — 키 활성화 시 22언어×549건 배치</t>
+          <t>notification_permission_dialog</t>
         </is>
       </c>
       <c r="F89" s="17" t="inlineStr">
@@ -3866,29 +3790,29 @@
       <c r="G89" s="16" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
         </is>
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>i18n</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
-          <t>남은</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>DeepL batch 실행</t>
+          <t>P10 — mobile 알림 라우팅</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr">
         <is>
-          <t>11개 언어 batch 번역 (현재 ko만)</t>
+          <t>알림 종류별 화면 이동 (coupon→쿠폰함, chat→채팅)</t>
         </is>
       </c>
       <c r="F90" s="21" t="inlineStr">
@@ -3896,21 +3820,17 @@
           <t>⬜</t>
         </is>
       </c>
-      <c r="G90" s="16" t="inlineStr">
-        <is>
-          <t>DeepL 키 활성화 후</t>
-        </is>
-      </c>
+      <c r="G90" s="16" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B91" s="15" t="inlineStr">
-        <is>
-          <t>정책/약관</t>
+      <c r="A91" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
+        <is>
+          <t>알림</t>
         </is>
       </c>
       <c r="C91" s="16" t="inlineStr">
@@ -3920,12 +3840,12 @@
       </c>
       <c r="D91" s="16" t="inlineStr">
         <is>
-          <t>policies API + 8 KIND</t>
+          <t>provider Notifications UI 골격</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>terms·privacy·location·marketing·push·camera·storage·third_party·age14 등록·버전관리</t>
+          <t>받은 알림 + 시스템 공지 UI, mockInbox 14건</t>
         </is>
       </c>
       <c r="F91" s="17" t="inlineStr">
@@ -3936,41 +3856,37 @@
       <c r="G91" s="16" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
+      <c r="A92" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
         </is>
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>정책/약관</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>mobile policy_view</t>
+          <t>P10 — provider Notifications 실연동</t>
         </is>
       </c>
       <c r="E92" s="16" t="inlineStr">
         <is>
-          <t>약관 본문 + 푸터·설정·동의 흐름 진입</t>
-        </is>
-      </c>
-      <c r="F92" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G92" s="16" t="inlineStr">
-        <is>
-          <t>?lang=ko 강제 → P13</t>
-        </is>
-      </c>
+          <t>mockInbox → /api/notifications 실연동</t>
+        </is>
+      </c>
+      <c r="F92" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="19" t="inlineStr">
@@ -3980,27 +3896,27 @@
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>정책/약관</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C93" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D93" s="16" t="inlineStr">
         <is>
-          <t>provider policy_view</t>
+          <t>P10 — provider 웹 푸시 통합</t>
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr">
         <is>
-          <t>약관 본문 노출</t>
-        </is>
-      </c>
-      <c r="F93" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
+          <t>브라우저 Web Push (자체구축, VAPID)</t>
+        </is>
+      </c>
+      <c r="F93" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
         </is>
       </c>
       <c r="G93" s="16" t="inlineStr"/>
@@ -4013,7 +3929,7 @@
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>정책/약관</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
@@ -4023,12 +3939,12 @@
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>admin Policies CRUD</t>
+          <t>admin 공지 CRUD + 발송</t>
         </is>
       </c>
       <c r="E94" s="16" t="inlineStr">
         <is>
-          <t>약관 등록·버전 발행 UI</t>
+          <t>Announcements CRUD + 푸시 발송 통합</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
@@ -4041,82 +3957,82 @@
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B95" s="16" t="inlineStr">
-        <is>
-          <t>정책/약관</t>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>WiFi (1회 연결)</t>
         </is>
       </c>
       <c r="C95" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D95" s="16" t="inlineStr">
         <is>
-          <t>P13 — 환불·청소년·쿠키 3종</t>
+          <t>wifi_profiles 기본</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr">
         <is>
-          <t>BE policy KIND 추가 + admin Policies + mobile/provider 노출</t>
-        </is>
-      </c>
-      <c r="F95" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G95" s="16" t="inlineStr">
-        <is>
-          <t>C14 해소</t>
-        </is>
-      </c>
+          <t>wifi_profiles 테이블 + CRUD API</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G95" s="16" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="18" t="inlineStr">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>WiFi (1회 연결)</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>BLE 핸드셰이크 API</t>
+        </is>
+      </c>
+      <c r="E96" s="16" t="inlineStr">
+        <is>
+          <t>/api/beacon/wifi handshake (LIMIT 1)</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="inlineStr">
+        <is>
+          <t>묶음 반환 확장 P15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="18" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B96" s="15" t="inlineStr">
-        <is>
-          <t>디자인 시스템</t>
-        </is>
-      </c>
-      <c r="C96" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>mobile PwTheme + 보라</t>
-        </is>
-      </c>
-      <c r="E96" s="16" t="inlineStr">
-        <is>
-          <t>PwTheme 다크 + Pw* 위젯 13종 (4종은 P1에서 추가)</t>
-        </is>
-      </c>
-      <c r="F96" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G96" s="16" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>디자인 시스템</t>
+          <t>WiFi (1회 연결)</t>
         </is>
       </c>
       <c r="C97" s="16" t="inlineStr">
@@ -4126,12 +4042,12 @@
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>provider 다크 + 녹색</t>
+          <t>mobile iOS native plugin</t>
         </is>
       </c>
       <c r="E97" s="16" t="inlineStr">
         <is>
-          <t>provider 디자인 시스템 통합 PR #66~#87</t>
+          <t>NEHotspotConfiguration 자동 가입 요청 (PR #49)</t>
         </is>
       </c>
       <c r="F97" s="17" t="inlineStr">
@@ -4142,14 +4058,14 @@
       <c r="G97" s="16" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
         </is>
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>디자인 시스템</t>
+          <t>WiFi (1회 연결)</t>
         </is>
       </c>
       <c r="C98" s="16" t="inlineStr">
@@ -4159,12 +4075,12 @@
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>admin 다크 + 블루</t>
+          <t>mobile Android native plugin</t>
         </is>
       </c>
       <c r="E98" s="16" t="inlineStr">
         <is>
-          <t>admin 다크 톤 통합 PR #65</t>
+          <t>WifiNetworkSuggestion 자동 가입</t>
         </is>
       </c>
       <c r="F98" s="17" t="inlineStr">
@@ -4182,22 +4098,22 @@
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>디자인 시스템</t>
+          <t>WiFi (1회 연결)</t>
         </is>
       </c>
       <c r="C99" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 ✅</t>
+          <t>이전 완료</t>
         </is>
       </c>
       <c r="D99" s="16" t="inlineStr">
         <is>
-          <t>P1 — mobile 기반 단일화</t>
+          <t>mobile WifiConnectScreen</t>
         </is>
       </c>
       <c r="E99" s="16" t="inlineStr">
         <is>
-          <t>테마 단일화 + 시스템 폰트 + Pw* 4종 신규(Radio·Checkbox·Dropdown·Chip)</t>
+          <t>BLE 핸드셰이크 → OS 자동 가입 트리거</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr">
@@ -4215,364 +4131,360 @@
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>디자인 시스템</t>
+          <t>WiFi (1회 연결)</t>
         </is>
       </c>
       <c r="C100" s="16" t="inlineStr">
         <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D100" s="16" t="inlineStr">
+        <is>
+          <t>provider WifiSettings UI</t>
+        </is>
+      </c>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>등록·수정·비활성 UI 완성</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G100" s="16" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B101" s="16" t="inlineStr">
+        <is>
+          <t>WiFi (1회 연결)</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
           <t>Phase 1 ✅</t>
         </is>
       </c>
-      <c r="D100" s="16" t="inlineStr">
-        <is>
-          <t>P3 — 웹 공용 모달</t>
-        </is>
-      </c>
-      <c r="E100" s="16" t="inlineStr">
-        <is>
-          <t>alert/confirm 33곳 → useDialog() + 색 토큰 정합 (provider 16 + admin 17)</t>
-        </is>
-      </c>
-      <c r="F100" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G100" s="16" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="20" t="inlineStr">
+      <c r="D101" s="16" t="inlineStr">
+        <is>
+          <t>P6 — runOcrMock 제거</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>WifiSettings·ServiceRequest 가짜 OCR 자동입력 삭제</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G101" s="16" t="inlineStr">
+        <is>
+          <t>심의 reject 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>WiFi (1회 연결)</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D102" s="16" t="inlineStr">
+        <is>
+          <t>P6 — 사진 첨부 재정의</t>
+        </is>
+      </c>
+      <c r="E102" s="16" t="inlineStr">
+        <is>
+          <t>사진 = 입력 확인용 참고 첨부 (정직한 안내문구)</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C103" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D103" s="16" t="inlineStr">
+        <is>
+          <t>P14 — 데이터 모델 재설계</t>
+        </is>
+      </c>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>wifi_profiles 확장 + beacon_wifi·units·wifi_access_grant·devices 신규</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G103" s="16" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>P14 — beacons.role 컬럼 추가</t>
+        </is>
+      </c>
+      <c r="E104" s="16" t="inlineStr">
+        <is>
+          <t>wifi / cashier 구분</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D105" s="16" t="inlineStr">
+        <is>
+          <t>P15 — handshake 묶음 반환</t>
+        </is>
+      </c>
+      <c r="E105" s="16" t="inlineStr">
+        <is>
+          <t>LIMIT 1 제거 → 매장 WiFi 묶음</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G105" s="16" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D106" s="16" t="inlineStr">
+        <is>
+          <t>P15 — WifiSettings 실연동 + 비콘 role UI</t>
+        </is>
+      </c>
+      <c r="E106" s="16" t="inlineStr">
+        <is>
+          <t>실 API 연동 + 비콘 role 선택</t>
+        </is>
+      </c>
+      <c r="F106" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G106" s="16" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
         <is>
           <t>슈퍼어드민</t>
         </is>
       </c>
-      <c r="B101" s="15" t="inlineStr">
-        <is>
-          <t>대시보드·통계</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D101" s="16" t="inlineStr">
-        <is>
-          <t>admin 기본 7페이지</t>
-        </is>
-      </c>
-      <c r="E101" s="16" t="inlineStr">
-        <is>
-          <t>Login + Dashboard + Beacons + Approvals + Battery + Announcements + Stores</t>
-        </is>
-      </c>
-      <c r="F101" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G101" s="16" t="inlineStr">
-        <is>
-          <t>PR #36~#38</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B102" s="16" t="inlineStr">
-        <is>
-          <t>대시보드·통계</t>
-        </is>
-      </c>
-      <c r="C102" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D102" s="16" t="inlineStr">
-        <is>
-          <t>admin Payments·Subscriptions·환불</t>
-        </is>
-      </c>
-      <c r="E102" s="16" t="inlineStr">
-        <is>
-          <t>결제/구독 관리 + 환불 모달 — 실 API 연동</t>
-        </is>
-      </c>
-      <c r="F102" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G102" s="16" t="inlineStr">
-        <is>
-          <t>PR #39</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B103" s="16" t="inlineStr">
-        <is>
-          <t>대시보드·통계</t>
-        </is>
-      </c>
-      <c r="C103" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D103" s="16" t="inlineStr">
-        <is>
-          <t>admin Policies·Translations·Audit·Reports</t>
-        </is>
-      </c>
-      <c r="E103" s="16" t="inlineStr">
-        <is>
-          <t>약관·번역·감사·신고 관리</t>
-        </is>
-      </c>
-      <c r="F103" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G103" s="16" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B104" s="16" t="inlineStr">
-        <is>
-          <t>대시보드·통계</t>
-        </is>
-      </c>
-      <c r="C104" s="16" t="inlineStr">
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C107" s="16" t="inlineStr">
         <is>
           <t>Phase 1 — 남은</t>
         </is>
       </c>
-      <c r="D104" s="16" t="inlineStr">
-        <is>
-          <t>P11 — Dashboard 가짜데이터 제거</t>
-        </is>
-      </c>
-      <c r="E104" s="16" t="inlineStr">
-        <is>
-          <t>실 통계 API 연동</t>
-        </is>
-      </c>
-      <c r="F104" s="21" t="inlineStr">
+      <c r="D107" s="16" t="inlineStr">
+        <is>
+          <t>P15 — admin WiFi 등록 신규</t>
+        </is>
+      </c>
+      <c r="E107" s="16" t="inlineStr">
+        <is>
+          <t>슈퍼어드민 WiFi 등록 화면 신규</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G104" s="16" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B105" s="16" t="inlineStr">
-        <is>
-          <t>대시보드·통계</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
+      <c r="G107" s="16" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
         <is>
           <t>Phase 1 — 남은</t>
         </is>
       </c>
-      <c r="D105" s="16" t="inlineStr">
-        <is>
-          <t>P11 — StaffMonitor·CouponStats placeholder</t>
-        </is>
-      </c>
-      <c r="E105" s="16" t="inlineStr">
-        <is>
-          <t>실 데이터 연동</t>
-        </is>
-      </c>
-      <c r="F105" s="21" t="inlineStr">
+      <c r="D108" s="16" t="inlineStr">
+        <is>
+          <t>P16 — 비콘→WiFi 묶음 fetch + 캐시</t>
+        </is>
+      </c>
+      <c r="E108" s="16" t="inlineStr">
+        <is>
+          <t>클라이언트 캐시 전략</t>
+        </is>
+      </c>
+      <c r="F108" s="21" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G105" s="16" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B106" s="16" t="inlineStr">
-        <is>
-          <t>대시보드·통계</t>
-        </is>
-      </c>
-      <c r="C106" s="16" t="inlineStr">
+      <c r="G108" s="16" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C109" s="16" t="inlineStr">
         <is>
           <t>Phase 1 — 남은</t>
         </is>
       </c>
-      <c r="D106" s="16" t="inlineStr">
-        <is>
-          <t>P20 — app-versions UI</t>
-        </is>
-      </c>
-      <c r="E106" s="16" t="inlineStr">
-        <is>
-          <t>백엔드 완성, admin UI만 신규</t>
-        </is>
-      </c>
-      <c r="F106" s="21" t="inlineStr">
+      <c r="D109" s="16" t="inlineStr">
+        <is>
+          <t>P16 — BSSID 검증</t>
+        </is>
+      </c>
+      <c r="E109" s="16" t="inlineStr">
+        <is>
+          <t>연결 후 BSSID 매칭 확인</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G106" s="16" t="inlineStr">
-        <is>
-          <t>C11 해소</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B107" s="15" t="inlineStr">
-        <is>
-          <t>직원 관리</t>
-        </is>
-      </c>
-      <c r="C107" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D107" s="16" t="inlineStr">
-        <is>
-          <t>백엔드 staff API</t>
-        </is>
-      </c>
-      <c r="E107" s="16" t="inlineStr">
-        <is>
-          <t>직원 초대/권한/관리 백엔드</t>
-        </is>
-      </c>
-      <c r="F107" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G107" s="16" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B108" s="16" t="inlineStr">
-        <is>
-          <t>직원 관리</t>
-        </is>
-      </c>
-      <c r="C108" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D108" s="16" t="inlineStr">
-        <is>
-          <t>provider StaffManagement UI</t>
-        </is>
-      </c>
-      <c r="E108" s="16" t="inlineStr">
-        <is>
-          <t>직원 목록·초대·권한 UI 완성, 데이터는 mock</t>
-        </is>
-      </c>
-      <c r="F108" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G108" s="16" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B109" s="16" t="inlineStr">
-        <is>
-          <t>직원 관리</t>
-        </is>
-      </c>
-      <c r="C109" s="16" t="inlineStr">
+      <c r="G109" s="16" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
         <is>
           <t>Phase 1 — 남은</t>
         </is>
       </c>
-      <c r="D109" s="16" t="inlineStr">
-        <is>
-          <t>P11 — provider StaffManagement 실연동</t>
-        </is>
-      </c>
-      <c r="E109" s="16" t="inlineStr">
-        <is>
-          <t>mock → 실 staff API 연동</t>
-        </is>
-      </c>
-      <c r="F109" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G109" s="16" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B110" s="16" t="inlineStr">
-        <is>
-          <t>직원 관리</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>P11 — admin StaffMonitor 실연동</t>
+          <t>P16 — "WiFi 변경됨" 흐름 + 손님 자동/승인</t>
         </is>
       </c>
       <c r="E110" s="16" t="inlineStr">
         <is>
-          <t>시설별 직원 모니터링</t>
+          <t>비콘 이동 감지 → 자동 전환</t>
         </is>
       </c>
       <c r="F110" s="21" t="inlineStr">
@@ -4588,420 +4500,404 @@
           <t>사용자</t>
         </is>
       </c>
-      <c r="B111" s="15" t="inlineStr">
-        <is>
-          <t>심의 직격</t>
+      <c r="B111" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
         </is>
       </c>
       <c r="C111" s="16" t="inlineStr">
         <is>
-          <t>이전 완료</t>
+          <t>Phase 1 — 남은</t>
         </is>
       </c>
       <c r="D111" s="16" t="inlineStr">
         <is>
-          <t>consent 단계 + 동의</t>
+          <t>P17 — .mobileconfig 다건 설치</t>
         </is>
       </c>
       <c r="E111" s="16" t="inlineStr">
         <is>
-          <t>8 KIND 동의 + 미성년자 보호 + 약관 본문</t>
-        </is>
-      </c>
-      <c r="F111" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G111" s="16" t="inlineStr">
-        <is>
-          <t>placeholder 노출 버그</t>
-        </is>
-      </c>
+          <t>.mobileconfig 생성·다건 설치 (서명은 인증서 후)</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G111" s="16" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="18" t="inlineStr">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C112" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
+          <t>P18 — credential_mode managed</t>
+        </is>
+      </c>
+      <c r="E112" s="16" t="inlineStr">
+        <is>
+          <t>비번 교체 리마인드 + 인가 손님 자동 전파 + 알림 연동</t>
+        </is>
+      </c>
+      <c r="F112" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G112" s="16" t="inlineStr">
+        <is>
+          <t>v1 flag 비공개</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B113" s="16" t="inlineStr">
+        <is>
+          <t>WiFi 로밍</t>
+        </is>
+      </c>
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D113" s="16" t="inlineStr">
+        <is>
+          <t>P19 — units/grant 관리 UI</t>
+        </is>
+      </c>
+      <c r="E113" s="16" t="inlineStr">
+        <is>
+          <t>호실·자리 시간제 권한 UI (admin/provider)</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G113" s="16" t="inlineStr">
+        <is>
+          <t>v1 flag 비공개</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B114" s="15" t="inlineStr">
+        <is>
+          <t>비콘</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D114" s="16" t="inlineStr">
+        <is>
+          <t>beacons lifecycle</t>
+        </is>
+      </c>
+      <c r="E114" s="16" t="inlineStr">
+        <is>
+          <t>inventory → active → inactive/lost 상태 전이 API</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G114" s="16" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
+          <t>비콘</t>
+        </is>
+      </c>
+      <c r="C115" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D115" s="16" t="inlineStr">
+        <is>
+          <t>비콘 claim API</t>
+        </is>
+      </c>
+      <c r="E115" s="16" t="inlineStr">
+        <is>
+          <t>시설 가입 후 비콘 SN 클레임</t>
+        </is>
+      </c>
+      <c r="F115" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G115" s="16" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>비콘</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D116" s="16" t="inlineStr">
+        <is>
+          <t>admin Beacons 인벤토리</t>
+        </is>
+      </c>
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>CSV 입고 + claim 모니터 + 배터리/펌웨어 표시</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G116" s="16" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B117" s="16" t="inlineStr">
+        <is>
+          <t>비콘</t>
+        </is>
+      </c>
+      <c r="C117" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="inlineStr">
+        <is>
+          <t>provider 비콘 claim UI</t>
+        </is>
+      </c>
+      <c r="E117" s="16" t="inlineStr">
+        <is>
+          <t>StoreInfo 내 claim + listBeacons</t>
+        </is>
+      </c>
+      <c r="F117" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G117" s="16" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B118" s="15" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>translations 테이블 + API</t>
+        </is>
+      </c>
+      <c r="E118" s="16" t="inlineStr">
+        <is>
+          <t>GET /api/i18n/{lang}</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G118" s="16" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D119" s="16" t="inlineStr">
+        <is>
+          <t>DeepL 통합 모듈</t>
+        </is>
+      </c>
+      <c r="E119" s="16" t="inlineStr">
+        <is>
+          <t>translator.py — DeepL/Google/Stub provider</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G119" s="16" t="inlineStr">
+        <is>
+          <t>키 활성화 후 batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>admin i18n CRUD</t>
+        </is>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>키별 다국어 입력·자동번역 트리거</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G120" s="16" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="18" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B112" s="16" t="inlineStr">
-        <is>
-          <t>심의 직격</t>
-        </is>
-      </c>
-      <c r="C112" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D112" s="16" t="inlineStr">
-        <is>
-          <t>settings 화면</t>
-        </is>
-      </c>
-      <c r="E112" s="16" t="inlineStr">
-        <is>
-          <t>계정·알림·약관·고객지원·회원탈퇴</t>
-        </is>
-      </c>
-      <c r="F112" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G112" s="16" t="inlineStr">
-        <is>
-          <t>dev API URL 노출 + 앱 버전 하드코딩</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="18" t="inlineStr">
+      <c r="B121" s="16" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="C121" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D121" s="16" t="inlineStr">
+        <is>
+          <t>mobile supportedLocales 7개 → 12개</t>
+        </is>
+      </c>
+      <c r="E121" s="16" t="inlineStr">
+        <is>
+          <t>P2 이전 7개, 이후 12개로 확장</t>
+        </is>
+      </c>
+      <c r="F121" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G121" s="16" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="18" t="inlineStr">
         <is>
           <t>사용자</t>
         </is>
       </c>
-      <c r="B113" s="16" t="inlineStr">
-        <is>
-          <t>심의 직격</t>
-        </is>
-      </c>
-      <c r="C113" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D113" s="16" t="inlineStr">
-        <is>
-          <t>P12 — consent placeholder 제거</t>
-        </is>
-      </c>
-      <c r="E113" s="16" t="inlineStr">
-        <is>
-          <t>placeholder 본문 노출 버그 수정</t>
-        </is>
-      </c>
-      <c r="F113" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G113" s="16" t="inlineStr">
-        <is>
-          <t>심의 reject 방지</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B114" s="16" t="inlineStr">
-        <is>
-          <t>심의 직격</t>
-        </is>
-      </c>
-      <c r="C114" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D114" s="16" t="inlineStr">
-        <is>
-          <t>P12 — 동의 로드 실패 복구</t>
-        </is>
-      </c>
-      <c r="E114" s="16" t="inlineStr">
-        <is>
-          <t>네트워크 오류 시 재시도/안내</t>
-        </is>
-      </c>
-      <c r="F114" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G114" s="16" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B115" s="16" t="inlineStr">
-        <is>
-          <t>심의 직격</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D115" s="16" t="inlineStr">
-        <is>
-          <t>P12 — settings dev 정보 제거 + 앱 버전 동적</t>
-        </is>
-      </c>
-      <c r="E115" s="16" t="inlineStr">
-        <is>
-          <t>API URL 제거 + package_info_plus</t>
-        </is>
-      </c>
-      <c r="F115" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G115" s="16" t="inlineStr">
-        <is>
-          <t>C9 해소</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="14" t="inlineStr">
-        <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B116" s="15" t="inlineStr">
-        <is>
-          <t>앱 버전관리</t>
-        </is>
-      </c>
-      <c r="C116" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D116" s="16" t="inlineStr">
-        <is>
-          <t>BE routes/version.py + app_versions</t>
-        </is>
-      </c>
-      <c r="E116" s="16" t="inlineStr">
-        <is>
-          <t>GET/PUT /api/admin/app-versions + 모바일 GET /api/version</t>
-        </is>
-      </c>
-      <c r="F116" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G116" s="16" t="inlineStr">
-        <is>
-          <t>코드 완성 — admin UI만 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="20" t="inlineStr">
-        <is>
-          <t>슈퍼어드민</t>
-        </is>
-      </c>
-      <c r="B117" s="16" t="inlineStr">
-        <is>
-          <t>앱 버전관리</t>
-        </is>
-      </c>
-      <c r="C117" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D117" s="16" t="inlineStr">
-        <is>
-          <t>P20 — admin app-versions UI</t>
-        </is>
-      </c>
-      <c r="E117" s="16" t="inlineStr">
-        <is>
-          <t>버전 등록·강제업데이트/권장 토글·OS별</t>
-        </is>
-      </c>
-      <c r="F117" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G117" s="16" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B118" s="16" t="inlineStr">
-        <is>
-          <t>앱 버전관리</t>
-        </is>
-      </c>
-      <c r="C118" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D118" s="16" t="inlineStr">
-        <is>
-          <t>P20 — mobile 최소버전 게이트</t>
-        </is>
-      </c>
-      <c r="E118" s="16" t="inlineStr">
-        <is>
-          <t>splash 버전 체크 → 강제 업데이트 모달</t>
-        </is>
-      </c>
-      <c r="F118" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G118" s="16" t="inlineStr">
-        <is>
-          <t>일부 처리 존재</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B119" s="15" t="inlineStr">
-        <is>
-          <t>심의 메타</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D119" s="16" t="inlineStr">
-        <is>
-          <t>P21 — iOS PrivacyInfo.xcprivacy</t>
-        </is>
-      </c>
-      <c r="E119" s="16" t="inlineStr">
-        <is>
-          <t>iOS 17.4+ 필수 — 데이터 수집/추적 명시</t>
-        </is>
-      </c>
-      <c r="F119" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G119" s="16" t="inlineStr">
-        <is>
-          <t>심의 reject 방지</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B120" s="16" t="inlineStr">
-        <is>
-          <t>심의 메타</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>P21 — Bundle ID 확정</t>
-        </is>
-      </c>
-      <c r="E120" s="16" t="inlineStr">
-        <is>
-          <t>co.triggersoft.pathwave 등 최종</t>
-        </is>
-      </c>
-      <c r="F120" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G120" s="16" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B121" s="16" t="inlineStr">
-        <is>
-          <t>심의 메타</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1 — 남은</t>
-        </is>
-      </c>
-      <c r="D121" s="16" t="inlineStr">
-        <is>
-          <t>P21 — Android Photo Picker</t>
-        </is>
-      </c>
-      <c r="E121" s="16" t="inlineStr">
-        <is>
-          <t>Android 13+ 신규 권한 모델</t>
-        </is>
-      </c>
-      <c r="F121" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G121" s="16" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>심의 메타</t>
+          <t>i18n</t>
         </is>
       </c>
       <c r="C122" s="16" t="inlineStr">
         <is>
-          <t>Phase 1 — 남은</t>
+          <t>Phase 1 ✅</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>P21 — 계정삭제 웹 URL</t>
+          <t>P2 — mobile I18nService 통일</t>
         </is>
       </c>
       <c r="E122" s="16" t="inlineStr">
         <is>
-          <t>Google Play 정책 — 앱 외부 웹 URL 제공</t>
-        </is>
-      </c>
-      <c r="F122" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
+          <t>12 supportedLocales + 전 화면 t() 전환</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
       <c r="G122" s="16" t="inlineStr"/>
@@ -5009,451 +4905,1983 @@
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
         <is>
-          <t>공통-BE</t>
-        </is>
-      </c>
-      <c r="B123" s="15" t="inlineStr">
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="C123" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D123" s="16" t="inlineStr">
+        <is>
+          <t>P2 — ko 시드 550 + DeepL 스크립트</t>
+        </is>
+      </c>
+      <c r="E123" s="16" t="inlineStr">
+        <is>
+          <t>translations DB ko 203→550 시드 + translate_i18n_deepl.py</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G123" s="16" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>i18n</t>
+        </is>
+      </c>
+      <c r="C124" s="16" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>DeepL 11언어 batch 실행</t>
+        </is>
+      </c>
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>키 활성화 후 22언어 × 549건 자동번역</t>
+        </is>
+      </c>
+      <c r="F124" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G124" s="16" t="inlineStr">
+        <is>
+          <t>DeepL 키 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B125" s="15" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="C125" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D125" s="16" t="inlineStr">
+        <is>
+          <t>policies API + 8 KIND</t>
+        </is>
+      </c>
+      <c r="E125" s="16" t="inlineStr">
+        <is>
+          <t>버전 관리 + record_consents 감사 로그</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G125" s="16" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="C126" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>mobile policy_view_screen</t>
+        </is>
+      </c>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>약관 본문 뷰어</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G126" s="16" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="C127" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D127" s="16" t="inlineStr">
+        <is>
+          <t>provider policy_view</t>
+        </is>
+      </c>
+      <c r="E127" s="16" t="inlineStr">
+        <is>
+          <t>약관 본문 노출</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G127" s="16" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="C128" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>admin Policies CRUD</t>
+        </is>
+      </c>
+      <c r="E128" s="16" t="inlineStr">
+        <is>
+          <t>등록·버전 발행</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G128" s="16" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="C129" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D129" s="16" t="inlineStr">
+        <is>
+          <t>P13 — 환불·청소년·쿠키 3종 추가</t>
+        </is>
+      </c>
+      <c r="E129" s="16" t="inlineStr">
+        <is>
+          <t>BE policy KIND 추가</t>
+        </is>
+      </c>
+      <c r="F129" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G129" s="16" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="C130" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>P13 — provider 노출</t>
+        </is>
+      </c>
+      <c r="E130" s="16" t="inlineStr">
+        <is>
+          <t>신규 3종 노출 + 동의 흐름</t>
+        </is>
+      </c>
+      <c r="F130" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G130" s="16" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B131" s="16" t="inlineStr">
+        <is>
+          <t>정책/약관</t>
+        </is>
+      </c>
+      <c r="C131" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D131" s="16" t="inlineStr">
+        <is>
+          <t>P13 — policy_view 언어 정합</t>
+        </is>
+      </c>
+      <c r="E131" s="16" t="inlineStr">
+        <is>
+          <t>?lang=ko 강제 → 사용자 언어로</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G131" s="16" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B132" s="15" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>mobile PwTheme + 보라</t>
+        </is>
+      </c>
+      <c r="E132" s="16" t="inlineStr">
+        <is>
+          <t>PwTheme 다크 + Pw* 위젯 9종</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G132" s="16" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="C133" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D133" s="16" t="inlineStr">
+        <is>
+          <t>P1 — mobile 단일화 + Pw* 4종 추가</t>
+        </is>
+      </c>
+      <c r="E133" s="16" t="inlineStr">
+        <is>
+          <t>테마 단일화 + 시스템 폰트 + Radio·Checkbox·Dropdown·Chip</t>
+        </is>
+      </c>
+      <c r="F133" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G133" s="16" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="C134" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>provider 다크 + 녹색</t>
+        </is>
+      </c>
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>PR #66~#87 통합</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G134" s="16" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="C135" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D135" s="16" t="inlineStr">
+        <is>
+          <t>P3 — provider 공용 모달</t>
+        </is>
+      </c>
+      <c r="E135" s="16" t="inlineStr">
+        <is>
+          <t>alert/confirm 16곳 → useDialog()</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G135" s="16" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D136" s="16" t="inlineStr">
+        <is>
+          <t>admin 다크 + 블루</t>
+        </is>
+      </c>
+      <c r="E136" s="16" t="inlineStr">
+        <is>
+          <t>PR #65</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G136" s="16" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B137" s="16" t="inlineStr">
+        <is>
+          <t>디자인 시스템</t>
+        </is>
+      </c>
+      <c r="C137" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 ✅</t>
+        </is>
+      </c>
+      <c r="D137" s="16" t="inlineStr">
+        <is>
+          <t>P3 — admin 공용 모달</t>
+        </is>
+      </c>
+      <c r="E137" s="16" t="inlineStr">
+        <is>
+          <t>alert/confirm 17곳 → useDialog()</t>
+        </is>
+      </c>
+      <c r="F137" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G137" s="16" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B138" s="15" t="inlineStr">
+        <is>
+          <t>대시보드·통계</t>
+        </is>
+      </c>
+      <c r="C138" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D138" s="16" t="inlineStr">
+        <is>
+          <t>admin 7페이지 베이스라인</t>
+        </is>
+      </c>
+      <c r="E138" s="16" t="inlineStr">
+        <is>
+          <t>Login + Dashboard + Beacons + Approvals + Battery + Announcements + Stores</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G138" s="16" t="inlineStr">
+        <is>
+          <t>PR #36~#38</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>대시보드·통계</t>
+        </is>
+      </c>
+      <c r="C139" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D139" s="16" t="inlineStr">
+        <is>
+          <t>admin Payments·Subscriptions·환불</t>
+        </is>
+      </c>
+      <c r="E139" s="16" t="inlineStr">
+        <is>
+          <t>결제/구독/환불 — 실 API 연동</t>
+        </is>
+      </c>
+      <c r="F139" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G139" s="16" t="inlineStr">
+        <is>
+          <t>PR #39</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>대시보드·통계</t>
+        </is>
+      </c>
+      <c r="C140" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D140" s="16" t="inlineStr">
+        <is>
+          <t>admin Policies·Translations·Audit·Reports</t>
+        </is>
+      </c>
+      <c r="E140" s="16" t="inlineStr">
+        <is>
+          <t>약관·번역·감사·신고 관리</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G140" s="16" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B141" s="16" t="inlineStr">
+        <is>
+          <t>대시보드·통계</t>
+        </is>
+      </c>
+      <c r="C141" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D141" s="16" t="inlineStr">
+        <is>
+          <t>admin 채팅 신고/차단 처리</t>
+        </is>
+      </c>
+      <c r="E141" s="16" t="inlineStr">
+        <is>
+          <t>abuse + chat_blocks (PR #142)</t>
+        </is>
+      </c>
+      <c r="F141" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G141" s="16" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>대시보드·통계</t>
+        </is>
+      </c>
+      <c r="C142" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D142" s="16" t="inlineStr">
+        <is>
+          <t>P11 — Dashboard 가짜데이터 제거</t>
+        </is>
+      </c>
+      <c r="E142" s="16" t="inlineStr">
+        <is>
+          <t>실 통계 API 연동</t>
+        </is>
+      </c>
+      <c r="F142" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G142" s="16" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B143" s="16" t="inlineStr">
+        <is>
+          <t>대시보드·통계</t>
+        </is>
+      </c>
+      <c r="C143" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D143" s="16" t="inlineStr">
+        <is>
+          <t>P11 — StaffMonitor 실연동</t>
+        </is>
+      </c>
+      <c r="E143" s="16" t="inlineStr">
+        <is>
+          <t>시설별 직원 모니터링</t>
+        </is>
+      </c>
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G143" s="16" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>대시보드·통계</t>
+        </is>
+      </c>
+      <c r="C144" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D144" s="16" t="inlineStr">
+        <is>
+          <t>P11 — CouponStats placeholder 해소</t>
+        </is>
+      </c>
+      <c r="E144" s="16" t="inlineStr">
+        <is>
+          <t>실 데이터 표시</t>
+        </is>
+      </c>
+      <c r="F144" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G144" s="16" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B145" s="16" t="inlineStr">
+        <is>
+          <t>대시보드·통계</t>
+        </is>
+      </c>
+      <c r="C145" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D145" s="16" t="inlineStr">
+        <is>
+          <t>P20 — app-versions UI 신규</t>
+        </is>
+      </c>
+      <c r="E145" s="16" t="inlineStr">
+        <is>
+          <t>BE 완성된 routes/version.py에 admin UI 연결</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G145" s="16" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B146" s="15" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="C146" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D146" s="16" t="inlineStr">
+        <is>
+          <t>staff API</t>
+        </is>
+      </c>
+      <c r="E146" s="16" t="inlineStr">
+        <is>
+          <t>초대/권한/관리 백엔드</t>
+        </is>
+      </c>
+      <c r="F146" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G146" s="16" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="inlineStr">
+        <is>
+          <t>provider StaffManagement UI 골격</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>목록·초대·권한 UI, 데이터 mock</t>
+        </is>
+      </c>
+      <c r="F147" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G147" s="16" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>직원 관리</t>
+        </is>
+      </c>
+      <c r="C148" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>P11 — provider StaffManagement 실연동</t>
+        </is>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>mock → 실 staff API</t>
+        </is>
+      </c>
+      <c r="F148" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G148" s="16" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B149" s="15" t="inlineStr">
+        <is>
+          <t>심의 직격</t>
+        </is>
+      </c>
+      <c r="C149" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="inlineStr">
+        <is>
+          <t>consent 단계</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>8 KIND 동의 + 미성년자 + 약관 본문</t>
+        </is>
+      </c>
+      <c r="F149" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G149" s="16" t="inlineStr">
+        <is>
+          <t>placeholder 노출 버그</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>심의 직격</t>
+        </is>
+      </c>
+      <c r="C150" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>settings 화면</t>
+        </is>
+      </c>
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>계정·알림·약관·고객지원·탈퇴</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G150" s="16" t="inlineStr">
+        <is>
+          <t>dev API URL 노출 + 버전 하드코딩</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>심의 직격</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>P12 — consent placeholder 제거</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>placeholder 본문 노출 수정</t>
+        </is>
+      </c>
+      <c r="F151" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G151" s="16" t="inlineStr">
+        <is>
+          <t>심의 reject 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>심의 직격</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D152" s="16" t="inlineStr">
+        <is>
+          <t>P12 — 동의 로드 실패 복구</t>
+        </is>
+      </c>
+      <c r="E152" s="16" t="inlineStr">
+        <is>
+          <t>네트워크 오류 시 재시도/안내</t>
+        </is>
+      </c>
+      <c r="F152" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G152" s="16" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>심의 직격</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D153" s="16" t="inlineStr">
+        <is>
+          <t>P12 — settings dev 정보 제거</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>API URL 노출 제거</t>
+        </is>
+      </c>
+      <c r="F153" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G153" s="16" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>심의 직격</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D154" s="16" t="inlineStr">
+        <is>
+          <t>P12 — 앱 버전 동적화</t>
+        </is>
+      </c>
+      <c r="E154" s="16" t="inlineStr">
+        <is>
+          <t>package_info_plus 도입 — 하드코딩 제거</t>
+        </is>
+      </c>
+      <c r="F154" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G154" s="16" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="14" t="inlineStr">
+        <is>
+          <t>Pathwave 서비스</t>
+        </is>
+      </c>
+      <c r="B155" s="15" t="inlineStr">
+        <is>
+          <t>앱 버전관리</t>
+        </is>
+      </c>
+      <c r="C155" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D155" s="16" t="inlineStr">
+        <is>
+          <t>BE routes/version.py + app_versions</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>admin GET/PUT + mobile GET /api/version</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G155" s="16" t="inlineStr">
+        <is>
+          <t>admin UI만 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>앱 버전관리</t>
+        </is>
+      </c>
+      <c r="C156" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D156" s="16" t="inlineStr">
+        <is>
+          <t>P20 — admin app-versions UI</t>
+        </is>
+      </c>
+      <c r="E156" s="16" t="inlineStr">
+        <is>
+          <t>버전 등록·강제/권장 토글·OS별</t>
+        </is>
+      </c>
+      <c r="F156" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G156" s="16" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B157" s="16" t="inlineStr">
+        <is>
+          <t>앱 버전관리</t>
+        </is>
+      </c>
+      <c r="C157" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D157" s="16" t="inlineStr">
+        <is>
+          <t>P20 — mobile 최소버전 게이트</t>
+        </is>
+      </c>
+      <c r="E157" s="16" t="inlineStr">
+        <is>
+          <t>splash 버전 체크 → 강제 업데이트 모달</t>
+        </is>
+      </c>
+      <c r="F157" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G157" s="16" t="inlineStr">
+        <is>
+          <t>일부 처리 존재</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B158" s="15" t="inlineStr">
+        <is>
+          <t>심의 메타</t>
+        </is>
+      </c>
+      <c r="C158" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="inlineStr">
+        <is>
+          <t>P21 — iOS PrivacyInfo.xcprivacy</t>
+        </is>
+      </c>
+      <c r="E158" s="16" t="inlineStr">
+        <is>
+          <t>iOS 17.4+ 필수 — 데이터 수집/추적 명시</t>
+        </is>
+      </c>
+      <c r="F158" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G158" s="16" t="inlineStr">
+        <is>
+          <t>심의 reject 방지</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>심의 메타</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D159" s="16" t="inlineStr">
+        <is>
+          <t>P21 — Bundle ID 확정</t>
+        </is>
+      </c>
+      <c r="E159" s="16" t="inlineStr">
+        <is>
+          <t>co.triggersoft.pathwave 등</t>
+        </is>
+      </c>
+      <c r="F159" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G159" s="16" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>심의 메타</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>P21 — Android Photo Picker</t>
+        </is>
+      </c>
+      <c r="E160" s="16" t="inlineStr">
+        <is>
+          <t>Android 13+ 신규 권한 모델</t>
+        </is>
+      </c>
+      <c r="F160" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G160" s="16" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B161" s="16" t="inlineStr">
+        <is>
+          <t>심의 메타</t>
+        </is>
+      </c>
+      <c r="C161" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1 — 남은</t>
+        </is>
+      </c>
+      <c r="D161" s="16" t="inlineStr">
+        <is>
+          <t>P21 — 계정삭제 웹 URL</t>
+        </is>
+      </c>
+      <c r="E161" s="16" t="inlineStr">
+        <is>
+          <t>Google Play 정책 — 외부 웹 URL</t>
+        </is>
+      </c>
+      <c r="F161" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G161" s="16" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="18" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="B162" s="15" t="inlineStr">
         <is>
           <t>회사 정보</t>
         </is>
       </c>
-      <c r="C123" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D123" s="16" t="inlineStr">
-        <is>
-          <t>company_info API (Phase M)</t>
-        </is>
-      </c>
-      <c r="E123" s="16" t="inlineStr">
-        <is>
-          <t>슈퍼어드민 입력값 GET /api/company-info</t>
-        </is>
-      </c>
-      <c r="F123" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G123" s="16" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="18" t="inlineStr">
-        <is>
-          <t>사용자</t>
-        </is>
-      </c>
-      <c r="B124" s="16" t="inlineStr">
+      <c r="C162" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D162" s="16" t="inlineStr">
+        <is>
+          <t>mobile PwFooter</t>
+        </is>
+      </c>
+      <c r="E162" s="16" t="inlineStr">
+        <is>
+          <t>CompanyInfoService 실연동</t>
+        </is>
+      </c>
+      <c r="F162" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G162" s="16" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="19" t="inlineStr">
+        <is>
+          <t>시설관리자</t>
+        </is>
+      </c>
+      <c r="B163" s="16" t="inlineStr">
         <is>
           <t>회사 정보</t>
         </is>
       </c>
-      <c r="C124" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D124" s="16" t="inlineStr">
-        <is>
-          <t>mobile PwFooter</t>
-        </is>
-      </c>
-      <c r="E124" s="16" t="inlineStr">
-        <is>
-          <t>CompanyInfoService 실연동 — DB값 + i18n fallback</t>
-        </is>
-      </c>
-      <c r="F124" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G124" s="16" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="19" t="inlineStr">
-        <is>
-          <t>시설관리자</t>
-        </is>
-      </c>
-      <c r="B125" s="16" t="inlineStr">
+      <c r="C163" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D163" s="16" t="inlineStr">
+        <is>
+          <t>provider PwFooter</t>
+        </is>
+      </c>
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t>CompanyInfoService 실연동</t>
+        </is>
+      </c>
+      <c r="F163" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G163" s="16" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="20" t="inlineStr">
+        <is>
+          <t>슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
         <is>
           <t>회사 정보</t>
         </is>
       </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D125" s="16" t="inlineStr">
-        <is>
-          <t>provider PwFooter</t>
-        </is>
-      </c>
-      <c r="E125" s="16" t="inlineStr">
-        <is>
-          <t>CompanyInfoService 실연동</t>
-        </is>
-      </c>
-      <c r="F125" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G125" s="16" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="20" t="inlineStr">
+      <c r="C164" s="16" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t>실 법인정보 입력</t>
+        </is>
+      </c>
+      <c r="E164" s="16" t="inlineStr">
+        <is>
+          <t>슈퍼어드민이 트리거소프트 실 정보 admin에서 입력</t>
+        </is>
+      </c>
+      <c r="F164" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G164" s="16" t="inlineStr">
+        <is>
+          <t>법인 등기 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B165" s="15" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="C165" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D165" s="16" t="inlineStr">
+        <is>
+          <t>BE 보안 강화</t>
+        </is>
+      </c>
+      <c r="E165" s="16" t="inlineStr">
+        <is>
+          <t>SECRET_KEY/AES_KEY ENV + CORS + rate-limit</t>
+        </is>
+      </c>
+      <c r="F165" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G165" s="16" t="inlineStr">
+        <is>
+          <t>PR #35</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="C166" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t>BE provider 추상화</t>
+        </is>
+      </c>
+      <c r="E166" s="16" t="inlineStr">
+        <is>
+          <t>PG(sim/toss) + Email + Push 추상화</t>
+        </is>
+      </c>
+      <c r="F166" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G166" s="16" t="inlineStr">
+        <is>
+          <t>키 활성화 시 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t>이전 완료</t>
+        </is>
+      </c>
+      <c r="D167" s="16" t="inlineStr">
+        <is>
+          <t>BE gunicorn/wsgi + Sentry + Postgres</t>
+        </is>
+      </c>
+      <c r="E167" s="16" t="inlineStr">
+        <is>
+          <t>프로덕션 배포 골격 + DATABASE_URL 분기</t>
+        </is>
+      </c>
+      <c r="F167" s="17" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G167" s="16" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1.5 — 남은</t>
+        </is>
+      </c>
+      <c r="D168" s="16" t="inlineStr">
+        <is>
+          <t>개발환경 서버 구축 (Mac mini 자체)</t>
+        </is>
+      </c>
+      <c r="E168" s="16" t="inlineStr">
+        <is>
+          <t>Mac mini 24/7 + Docker Postgres + Cloudflare Tunnel</t>
+        </is>
+      </c>
+      <c r="F168" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G168" s="16" t="inlineStr">
+        <is>
+          <t>메모리 권장 셋업</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B169" s="16" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="C169" s="16" t="inlineStr">
+        <is>
+          <t>Phase 1.5 — 남은</t>
+        </is>
+      </c>
+      <c r="D169" s="16" t="inlineStr">
+        <is>
+          <t>통합 테스트 (3콘솔 + mobile 실기기)</t>
+        </is>
+      </c>
+      <c r="E169" s="16" t="inlineStr">
+        <is>
+          <t>실 서버 + 실 키 + 3콘솔 + mobile walk-through</t>
+        </is>
+      </c>
+      <c r="F169" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G169" s="16" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t>운영 인프라</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t>운영 서버 배포</t>
+        </is>
+      </c>
+      <c r="E170" s="16" t="inlineStr">
+        <is>
+          <t>개발환경 검증 → 운영 전환 (Mac mini 또는 가비아 호스팅)</t>
+        </is>
+      </c>
+      <c r="F170" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G170" s="16" t="inlineStr">
+        <is>
+          <t>심의 제출 직전</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B171" s="15" t="inlineStr">
+        <is>
+          <t>자동화</t>
+        </is>
+      </c>
+      <c r="C171" s="16" t="inlineStr">
+        <is>
+          <t>남은 (Stage 1)</t>
+        </is>
+      </c>
+      <c r="D171" s="16" t="inlineStr">
+        <is>
+          <t>카톡 챗봇 — 자체 webhook</t>
+        </is>
+      </c>
+      <c r="E171" s="16" t="inlineStr">
+        <is>
+          <t>카카오 i 오픈빌더 무료 + Mac mini webhook 처리</t>
+        </is>
+      </c>
+      <c r="F171" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G171" s="16" t="inlineStr">
+        <is>
+          <t>메모리 — Mac mini 자체</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t>자동화</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="inlineStr">
+        <is>
+          <t>남은 (Stage 1)</t>
+        </is>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t>이메일 자동 응답 — 자체 분류</t>
+        </is>
+      </c>
+      <c r="E172" s="16" t="inlineStr">
+        <is>
+          <t>Mac mini Python 스크립트 + IMAP 폴링</t>
+        </is>
+      </c>
+      <c r="F172" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G172" s="16" t="inlineStr">
+        <is>
+          <t>메모리 services/customer_support_ai.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
+        <is>
+          <t>자동화</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
+        <is>
+          <t>남은 (Stage 2)</t>
+        </is>
+      </c>
+      <c r="D173" s="16" t="inlineStr">
+        <is>
+          <t>AI 응답 (자체 LLM 또는 OpenAI)</t>
+        </is>
+      </c>
+      <c r="E173" s="16" t="inlineStr">
+        <is>
+          <t>Mac mini Llama 양자화 또는 ChatGPT API (소규모)</t>
+        </is>
+      </c>
+      <c r="F173" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G173" s="16" t="inlineStr">
+        <is>
+          <t>대규모는 외부 API</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>자동화</t>
+        </is>
+      </c>
+      <c r="C174" s="16" t="inlineStr">
+        <is>
+          <t>남은 (Stage 2)</t>
+        </is>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t>SNS 자동 게시 — 자체 cron</t>
+        </is>
+      </c>
+      <c r="E174" s="16" t="inlineStr">
+        <is>
+          <t>Mac mini cron + Meta/Insta/YouTube/TikTok API 직접</t>
+        </is>
+      </c>
+      <c r="F174" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G174" s="16" t="inlineStr">
+        <is>
+          <t>Buffer 등 SaaS 대체</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
+        <is>
+          <t>자동화</t>
+        </is>
+      </c>
+      <c r="C175" s="16" t="inlineStr">
+        <is>
+          <t>남은 (Stage 2)</t>
+        </is>
+      </c>
+      <c r="D175" s="16" t="inlineStr">
+        <is>
+          <t>앱 스토어 리뷰 폴링 + AI 응답</t>
+        </is>
+      </c>
+      <c r="E175" s="16" t="inlineStr">
+        <is>
+          <t>Mac mini services/app_store_reviews.py + review_response_ai.py</t>
+        </is>
+      </c>
+      <c r="F175" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G175" s="16" t="inlineStr">
+        <is>
+          <t>메모리</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t>자동화</t>
+        </is>
+      </c>
+      <c r="C176" s="16" t="inlineStr">
+        <is>
+          <t>남은 (Stage 3)</t>
+        </is>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t>사용자 행동 시퀀스</t>
+        </is>
+      </c>
+      <c r="E176" s="16" t="inlineStr">
+        <is>
+          <t>백엔드 services/notification_sequence.py</t>
+        </is>
+      </c>
+      <c r="F176" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G176" s="16" t="inlineStr">
+        <is>
+          <t>출시 후</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="20" t="inlineStr">
         <is>
           <t>슈퍼어드민</t>
         </is>
       </c>
-      <c r="B126" s="16" t="inlineStr">
-        <is>
-          <t>회사 정보</t>
-        </is>
-      </c>
-      <c r="C126" s="16" t="inlineStr">
+      <c r="B177" s="16" t="inlineStr">
+        <is>
+          <t>자동화</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>남은 (Stage 2)</t>
+        </is>
+      </c>
+      <c r="D177" s="16" t="inlineStr">
+        <is>
+          <t>admin 자동화 대시보드</t>
+        </is>
+      </c>
+      <c r="E177" s="16" t="inlineStr">
+        <is>
+          <t>고객응대/마케팅 현황 — admin-web 메뉴 추가</t>
+        </is>
+      </c>
+      <c r="F177" s="21" t="inlineStr">
+        <is>
+          <t>⬜</t>
+        </is>
+      </c>
+      <c r="G177" s="16" t="inlineStr">
+        <is>
+          <t>Phase D</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="22" t="inlineStr">
+        <is>
+          <t>인프라</t>
+        </is>
+      </c>
+      <c r="B178" s="15" t="inlineStr">
+        <is>
+          <t>Phase 2~4</t>
+        </is>
+      </c>
+      <c r="C178" s="16" t="inlineStr">
         <is>
           <t>남은</t>
         </is>
       </c>
-      <c r="D126" s="16" t="inlineStr">
-        <is>
-          <t>실 법인정보 입력</t>
-        </is>
-      </c>
-      <c r="E126" s="16" t="inlineStr">
-        <is>
-          <t>슈퍼어드민이 트리거소프트 실 정보 admin에서 입력</t>
-        </is>
-      </c>
-      <c r="F126" s="21" t="inlineStr">
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t>W7 — 6 페르소나 테스트 시드</t>
+        </is>
+      </c>
+      <c r="E178" s="16" t="inlineStr">
+        <is>
+          <t>외국인/한국인/소규모/중대형/직원/슈퍼어드민</t>
+        </is>
+      </c>
+      <c r="F178" s="21" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G126" s="16" t="inlineStr">
-        <is>
-          <t>법인 등기 완료 — 등록만 남음</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="22" t="inlineStr">
+      <c r="G178" s="16" t="inlineStr">
+        <is>
+          <t>7월 중~하순</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="22" t="inlineStr">
         <is>
           <t>인프라</t>
         </is>
       </c>
-      <c r="B127" s="15" t="inlineStr">
-        <is>
-          <t>운영 인프라</t>
-        </is>
-      </c>
-      <c r="C127" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D127" s="16" t="inlineStr">
-        <is>
-          <t>BE 보안 강화</t>
-        </is>
-      </c>
-      <c r="E127" s="16" t="inlineStr">
-        <is>
-          <t>SECRET_KEY/AES_KEY ENV + CORS 화이트리스트 + rate-limit (PR #35)</t>
-        </is>
-      </c>
-      <c r="F127" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G127" s="16" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="inlineStr">
-        <is>
-          <t>운영 인프라</t>
-        </is>
-      </c>
-      <c r="C128" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>BE provider 추상화</t>
-        </is>
-      </c>
-      <c r="E128" s="16" t="inlineStr">
-        <is>
-          <t>PG(sim/toss) + Email(stub/sendgrid/smtp) + Push(stub/fcm/apns) 추상화</t>
-        </is>
-      </c>
-      <c r="F128" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G128" s="16" t="inlineStr">
-        <is>
-          <t>키 활성화 시 즉시 전환</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B129" s="16" t="inlineStr">
-        <is>
-          <t>운영 인프라</t>
-        </is>
-      </c>
-      <c r="C129" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D129" s="16" t="inlineStr">
-        <is>
-          <t>BE gunicorn/wsgi + Sentry</t>
-        </is>
-      </c>
-      <c r="E129" s="16" t="inlineStr">
-        <is>
-          <t>프로덕션 배포 골격 + Sentry 통합</t>
-        </is>
-      </c>
-      <c r="F129" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G129" s="16" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B130" s="16" t="inlineStr">
-        <is>
-          <t>운영 인프라</t>
-        </is>
-      </c>
-      <c r="C130" s="16" t="inlineStr">
-        <is>
-          <t>이전 완료</t>
-        </is>
-      </c>
-      <c r="D130" s="16" t="inlineStr">
-        <is>
-          <t>BE PostgreSQL 어댑터</t>
-        </is>
-      </c>
-      <c r="E130" s="16" t="inlineStr">
-        <is>
-          <t>DATABASE_URL ENV 자동 분기 (sqlite ↔ pg)</t>
-        </is>
-      </c>
-      <c r="F130" s="17" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="G130" s="16" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B131" s="16" t="inlineStr">
-        <is>
-          <t>운영 인프라</t>
-        </is>
-      </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1.5 — 남은</t>
-        </is>
-      </c>
-      <c r="D131" s="16" t="inlineStr">
-        <is>
-          <t>개발환경 서버 구축</t>
-        </is>
-      </c>
-      <c r="E131" s="16" t="inlineStr">
-        <is>
-          <t>국내 클라우드(가비아 G클라우드 등) + Postgres + 환경변수 키 주입</t>
-        </is>
-      </c>
-      <c r="F131" s="21" t="inlineStr">
+      <c r="B179" s="15" t="inlineStr">
+        <is>
+          <t>Phase 5</t>
+        </is>
+      </c>
+      <c r="C179" s="16" t="inlineStr">
+        <is>
+          <t>남은</t>
+        </is>
+      </c>
+      <c r="D179" s="16" t="inlineStr">
+        <is>
+          <t>스토어 메타데이터 + 빌드</t>
+        </is>
+      </c>
+      <c r="E179" s="16" t="inlineStr">
+        <is>
+          <t>iOS/Android 빌드 + 스크린샷 + 메타데이터(다국어) + 심의</t>
+        </is>
+      </c>
+      <c r="F179" s="21" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
-      <c r="G131" s="16" t="inlineStr">
-        <is>
-          <t>코드 완료 후 출시 전 단계</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B132" s="16" t="inlineStr">
-        <is>
-          <t>운영 인프라</t>
-        </is>
-      </c>
-      <c r="C132" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1.5 — 남은</t>
-        </is>
-      </c>
-      <c r="D132" s="16" t="inlineStr">
-        <is>
-          <t>통합 테스트 (3콘솔 + mobile)</t>
-        </is>
-      </c>
-      <c r="E132" s="16" t="inlineStr">
-        <is>
-          <t>실 서버 + 실 키 + 3콘솔 + mobile 실 기기 walk-through</t>
-        </is>
-      </c>
-      <c r="F132" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G132" s="16" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B133" s="16" t="inlineStr">
-        <is>
-          <t>운영 인프라</t>
-        </is>
-      </c>
-      <c r="C133" s="16" t="inlineStr">
-        <is>
-          <t>남은</t>
-        </is>
-      </c>
-      <c r="D133" s="16" t="inlineStr">
-        <is>
-          <t>운영 서버 배포</t>
-        </is>
-      </c>
-      <c r="E133" s="16" t="inlineStr">
-        <is>
-          <t>개발환경 검증 → 운영 서버 전환</t>
-        </is>
-      </c>
-      <c r="F133" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G133" s="16" t="inlineStr">
-        <is>
-          <t>심의 제출 직전</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B134" s="15" t="inlineStr">
-        <is>
-          <t>Phase 2~4 테스트</t>
-        </is>
-      </c>
-      <c r="C134" s="16" t="inlineStr">
-        <is>
-          <t>남은</t>
-        </is>
-      </c>
-      <c r="D134" s="16" t="inlineStr">
-        <is>
-          <t>W7 — 6 페르소나 테스트 시드</t>
-        </is>
-      </c>
-      <c r="E134" s="16" t="inlineStr">
-        <is>
-          <t>외국인/한국인/소규모/중대형/직원/슈퍼어드민 시나리오 + walk-through</t>
-        </is>
-      </c>
-      <c r="F134" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G134" s="16" t="inlineStr">
-        <is>
-          <t>7월 중순~하순</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="22" t="inlineStr">
-        <is>
-          <t>인프라</t>
-        </is>
-      </c>
-      <c r="B135" s="15" t="inlineStr">
-        <is>
-          <t>Phase 5 제출</t>
-        </is>
-      </c>
-      <c r="C135" s="16" t="inlineStr">
-        <is>
-          <t>남은</t>
-        </is>
-      </c>
-      <c r="D135" s="16" t="inlineStr">
-        <is>
-          <t>스토어 메타데이터 + 빌드</t>
-        </is>
-      </c>
-      <c r="E135" s="16" t="inlineStr">
-        <is>
-          <t>iOS/Android 빌드 + 스크린샷 + 메타데이터(다국어) + 심의 제출</t>
-        </is>
-      </c>
-      <c r="F135" s="21" t="inlineStr">
-        <is>
-          <t>⬜</t>
-        </is>
-      </c>
-      <c r="G135" s="16" t="inlineStr">
+      <c r="G179" s="16" t="inlineStr">
         <is>
           <t>7월 하순~8월 초</t>
         </is>
@@ -5478,7 +6906,7 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
@@ -5618,7 +7046,7 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>사용자·공통</t>
+          <t>사용자·Pathwave</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -5724,7 +7152,7 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>시설관리자·공통</t>
+          <t>시설관리자·Pathwave</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
@@ -5734,7 +7162,7 @@
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>DEV_AUTO_LOGIN env 게이트 + 실 로그인폼 + /forgot-password 정식</t>
+          <t>DEV_AUTO_LOGIN env + 실 로그인폼 + /forgot-password 정식</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
@@ -5763,7 +7191,7 @@
       </c>
       <c r="K5" s="25" t="inlineStr">
         <is>
-          <t>⚠ app.py 재시작 필요</t>
+          <t>⚠ app.py 재시작</t>
         </is>
       </c>
       <c r="L5" s="16" t="n"/>
@@ -5979,7 +7407,7 @@
       </c>
       <c r="K9" s="25" t="inlineStr">
         <is>
-          <t>번역=P8b, ⚠ app.py 재시작</t>
+          <t>번역=P8b, ⚠ 재시작</t>
         </is>
       </c>
       <c r="L9" s="16" t="n"/>
@@ -6101,7 +7529,7 @@
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>provider 실연동 + mobile 라우팅</t>
+          <t>provider 실연동 + mobile 라우팅 + 웹푸시 자체구축</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -6146,7 +7574,7 @@
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>Dashboard·StaffManagement 실연동</t>
+          <t>Dashboard·StaffManagement·CouponStats 실연동</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -6271,7 +7699,7 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>Pathwave</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
@@ -6281,7 +7709,7 @@
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>wifi_profiles 확장 + 신규 테이블</t>
+          <t>wifi_profiles 확장 + 신규 테이블 + beacons.role</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -6296,7 +7724,7 @@
       <c r="H16" s="24" t="inlineStr"/>
       <c r="I16" s="25" t="inlineStr">
         <is>
-          <t>2026-06-말~7월초</t>
+          <t>6/말~7/초</t>
         </is>
       </c>
       <c r="J16" s="25" t="inlineStr"/>
@@ -6326,7 +7754,7 @@
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>handshake 묶음 + admin 등록 + provider WifiSettings</t>
+          <t>handshake 묶음 + admin 등록 + provider 실연동</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -6341,7 +7769,7 @@
       <c r="H17" s="24" t="inlineStr"/>
       <c r="I17" s="25" t="inlineStr">
         <is>
-          <t>2026-07-초</t>
+          <t>7/초</t>
         </is>
       </c>
       <c r="J17" s="25" t="inlineStr"/>
@@ -6386,7 +7814,7 @@
       <c r="H18" s="24" t="inlineStr"/>
       <c r="I18" s="25" t="inlineStr">
         <is>
-          <t>2026-07-초</t>
+          <t>7/초</t>
         </is>
       </c>
       <c r="J18" s="25" t="inlineStr"/>
@@ -6431,7 +7859,7 @@
       <c r="H19" s="24" t="inlineStr"/>
       <c r="I19" s="25" t="inlineStr">
         <is>
-          <t>2026-07-중</t>
+          <t>7/중</t>
         </is>
       </c>
       <c r="J19" s="25" t="inlineStr"/>
@@ -6465,7 +7893,7 @@
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>비번 교체 리마인드 + 자동 전파</t>
+          <t>비번 교체 + 자동 전파</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -6480,13 +7908,13 @@
       <c r="H20" s="24" t="inlineStr"/>
       <c r="I20" s="25" t="inlineStr">
         <is>
-          <t>2026-07-중</t>
+          <t>7/중</t>
         </is>
       </c>
       <c r="J20" s="25" t="inlineStr"/>
       <c r="K20" s="25" t="inlineStr">
         <is>
-          <t>v1 flag 비공개</t>
+          <t>v1 flag</t>
         </is>
       </c>
       <c r="L20" s="16" t="n"/>
@@ -6514,7 +7942,7 @@
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>호실·자리 시간제 권한</t>
+          <t>호실·자리 권한</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -6529,13 +7957,13 @@
       <c r="H21" s="24" t="inlineStr"/>
       <c r="I21" s="25" t="inlineStr">
         <is>
-          <t>2026-07-중</t>
+          <t>7/중</t>
         </is>
       </c>
       <c r="J21" s="25" t="inlineStr"/>
       <c r="K21" s="25" t="inlineStr">
         <is>
-          <t>v1 flag 비공개</t>
+          <t>v1 flag</t>
         </is>
       </c>
       <c r="L21" s="16" t="n"/>
@@ -6578,7 +8006,7 @@
       <c r="H22" s="24" t="inlineStr"/>
       <c r="I22" s="25" t="inlineStr">
         <is>
-          <t>2026-07-중</t>
+          <t>7/중</t>
         </is>
       </c>
       <c r="J22" s="25" t="inlineStr"/>
@@ -6623,7 +8051,7 @@
       <c r="H23" s="24" t="inlineStr"/>
       <c r="I23" s="25" t="inlineStr">
         <is>
-          <t>2026-07-중</t>
+          <t>7/중</t>
         </is>
       </c>
       <c r="J23" s="25" t="inlineStr"/>
@@ -6668,7 +8096,7 @@
       <c r="H24" s="24" t="inlineStr"/>
       <c r="I24" s="25" t="inlineStr">
         <is>
-          <t>2026-07-초~중</t>
+          <t>7/초~중</t>
         </is>
       </c>
       <c r="J24" s="25" t="inlineStr"/>
@@ -6694,11 +8122,11 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -6854,7 +8282,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>2026-07-초~중</t>
+          <t>7/초~중</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
@@ -6881,7 +8309,7 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>2026-07-초~중</t>
+          <t>7/초~중</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr"/>
@@ -6904,7 +8332,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>2026-07-중</t>
+          <t>7/중</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr"/>
@@ -6912,12 +8340,12 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Phase 1.5 — 개발환경 구축</t>
+          <t>Phase 1.5 — Mac mini 개발환경 구축</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>국내 클라우드 서버 + Postgres + 환경변수 키 주입</t>
+          <t>Mac mini 24/7 + Docker Postgres + Cloudflare Tunnel + 환경변수 키 주입</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -6927,12 +8355,12 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>2026-07-중</t>
+          <t>7/중</t>
         </is>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>신규 — 운영 반영 전</t>
+          <t>메모리 권장 셋업</t>
         </is>
       </c>
     </row>
@@ -6954,14 +8382,10 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>2026-07-중~하순</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
+          <t>7/중~하순</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -6981,7 +8405,7 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>2026-07-하순</t>
+          <t>7/하순</t>
         </is>
       </c>
       <c r="E11" s="16" t="inlineStr"/>
@@ -7004,7 +8428,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>2026-07-하순</t>
+          <t>7/하순</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr"/>
@@ -7027,7 +8451,7 @@
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>2026-07-하순~8월 초</t>
+          <t>7/하순~8/초</t>
         </is>
       </c>
       <c r="E13" s="16" t="inlineStr"/>
@@ -7040,7 +8464,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>법인카드 수취 후 일괄</t>
+          <t>법인카드 수취 후 일괄 (던스 → Apple → 도메인 등)</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
